--- a/research/evaluation/Traton_valuation_FINAL.xlsx
+++ b/research/evaluation/Traton_valuation_FINAL.xlsx
@@ -3,19 +3,17 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FCFF &amp; DCF" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="WACC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Equity Bridge" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Multiples" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Football-Field" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Annahmen &amp; Herleitung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FCFF &amp; DCF" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="WACC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Equity Bridge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Multiples" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Football-Field" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'Equity Bridge'!$B$5:$B$11</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Equity Bridge'!$C$5:$C$11</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
@@ -36,7 +34,7 @@
     <numFmt numFmtId="174" formatCode="0.0\x"/>
     <numFmt numFmtId="175" formatCode="#,##0.00_);\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -172,13 +170,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00333333"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -215,8 +248,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -424,6 +467,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -431,7 +532,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="275">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -485,13 +586,11 @@
     <xf numFmtId="171" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="170" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="171" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="171" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="10" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="171" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="171" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="170" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -533,7 +632,6 @@
     <xf numFmtId="11" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="9" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="170" fontId="9" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -690,10 +788,6 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="1" xfId="1"/>
     <xf numFmtId="169" fontId="9" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -759,7 +853,6 @@
     <xf numFmtId="166" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="175" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -838,20 +931,44 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -876,51 +993,19 @@
     <xf numFmtId="171" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="172" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="170" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="175" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="170" fontId="9" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="8" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="9" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="169" fontId="9" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="8" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="170" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" pivotButton="0" quotePrefix="1" xfId="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="1" xfId="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -959,13 +1044,80 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Komma" xfId="1" builtinId="3"/>
+    <cellStyle name="Währung" xfId="2" builtinId="4"/>
+    <cellStyle name="Prozent" xfId="3" builtinId="5"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1006,29 +1158,6 @@
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
-      <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="it-IT"/>
-        </a:p>
-      </txPr>
     </title>
     <plotArea>
       <layout/>
@@ -1045,7 +1174,7 @@
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
-                  <v xml:space="preserve">low </v>
+                  <v>low</v>
                 </pt>
               </strCache>
             </strRef>
@@ -1086,7 +1215,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="it-IT"/>
               </a:p>
@@ -1106,16 +1235,16 @@
               <strCache>
                 <ptCount val="4"/>
                 <pt idx="0">
-                  <v>Placeholder1</v>
+                  <v>DCF (WACC 6.9-7.9%)</v>
                 </pt>
                 <pt idx="1">
-                  <v>Placeholder2</v>
+                  <v>EV/EBITDA FY+1 (peer range)</v>
                 </pt>
                 <pt idx="2">
-                  <v>Placeholder3</v>
+                  <v>EV/EBIT FY+1 (peer range)</v>
                 </pt>
                 <pt idx="3">
-                  <v>Placeholder4</v>
+                  <v>EV/Revenue FY+1 (peer range)</v>
                 </pt>
               </strCache>
             </strRef>
@@ -1126,6 +1255,18 @@
               <numCache>
                 <formatCode>0.00</formatCode>
                 <ptCount val="4"/>
+                <pt idx="0">
+                  <v>55.4</v>
+                </pt>
+                <pt idx="1">
+                  <v>48.7</v>
+                </pt>
+                <pt idx="2">
+                  <v>30.2</v>
+                </pt>
+                <pt idx="3">
+                  <v>34.3</v>
+                </pt>
               </numCache>
             </numRef>
           </val>
@@ -1163,16 +1304,16 @@
               <strCache>
                 <ptCount val="4"/>
                 <pt idx="0">
-                  <v>Placeholder1</v>
+                  <v>DCF (WACC 6.9-7.9%)</v>
                 </pt>
                 <pt idx="1">
-                  <v>Placeholder2</v>
+                  <v>EV/EBITDA FY+1 (peer range)</v>
                 </pt>
                 <pt idx="2">
-                  <v>Placeholder3</v>
+                  <v>EV/EBIT FY+1 (peer range)</v>
                 </pt>
                 <pt idx="3">
-                  <v>Placeholder4</v>
+                  <v>EV/Revenue FY+1 (peer range)</v>
                 </pt>
               </strCache>
             </strRef>
@@ -1183,6 +1324,18 @@
               <numCache>
                 <formatCode>0.00</formatCode>
                 <ptCount val="4"/>
+                <pt idx="0">
+                  <v>12.00000000000001</v>
+                </pt>
+                <pt idx="1">
+                  <v>32.2</v>
+                </pt>
+                <pt idx="2">
+                  <v>26.7</v>
+                </pt>
+                <pt idx="3">
+                  <v>72.90000000000001</v>
+                </pt>
               </numCache>
             </numRef>
           </val>
@@ -1196,7 +1349,7 @@
               <strCache>
                 <ptCount val="1"/>
                 <pt idx="0">
-                  <v xml:space="preserve">high </v>
+                  <v>high</v>
                 </pt>
               </strCache>
             </strRef>
@@ -1237,7 +1390,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="it-IT"/>
               </a:p>
@@ -1257,16 +1410,16 @@
               <strCache>
                 <ptCount val="4"/>
                 <pt idx="0">
-                  <v>Placeholder1</v>
+                  <v>DCF (WACC 6.9-7.9%)</v>
                 </pt>
                 <pt idx="1">
-                  <v>Placeholder2</v>
+                  <v>EV/EBITDA FY+1 (peer range)</v>
                 </pt>
                 <pt idx="2">
-                  <v>Placeholder3</v>
+                  <v>EV/EBIT FY+1 (peer range)</v>
                 </pt>
                 <pt idx="3">
-                  <v>Placeholder4</v>
+                  <v>EV/Revenue FY+1 (peer range)</v>
                 </pt>
               </strCache>
             </strRef>
@@ -1277,6 +1430,18 @@
               <numCache>
                 <formatCode>0.00</formatCode>
                 <ptCount val="4"/>
+                <pt idx="0">
+                  <v>67.40000000000001</v>
+                </pt>
+                <pt idx="1">
+                  <v>80.90000000000001</v>
+                </pt>
+                <pt idx="2">
+                  <v>56.9</v>
+                </pt>
+                <pt idx="3">
+                  <v>107.2</v>
+                </pt>
               </numCache>
             </numRef>
           </val>
@@ -1332,7 +1497,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="it-IT"/>
           </a:p>
@@ -1730,16 +1895,875 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB74"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15"/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" style="1" min="1" max="1"/>
-    <col width="36.28515625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="17.42578125" customWidth="1" style="1" min="3" max="6"/>
-    <col width="19.28515625" customWidth="1" style="1" min="7" max="7"/>
-    <col width="17.42578125" customWidth="1" style="1" min="8" max="22"/>
-    <col width="18.42578125" customWidth="1" style="1" min="23" max="23"/>
-    <col width="11" customWidth="1" style="1" min="24" max="16384"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="203" t="inlineStr">
+        <is>
+          <t>Annahmen &amp; Herleitung — Traton SE Bewertung (Stichtag 30.06.2026)</t>
+        </is>
+      </c>
+      <c r="B1" s="204" t="n"/>
+      <c r="C1" s="204" t="n"/>
+      <c r="D1" s="205" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="206" t="inlineStr">
+        <is>
+          <t>A · DCF- und Cashflow-Annahmen</t>
+        </is>
+      </c>
+      <c r="B3" s="204" t="n"/>
+      <c r="C3" s="204" t="n"/>
+      <c r="D3" s="205" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="207" t="inlineStr">
+        <is>
+          <t>Annahme</t>
+        </is>
+      </c>
+      <c r="B4" s="207" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="C4" s="207" t="inlineStr">
+        <is>
+          <t>Herleitung / Quelle</t>
+        </is>
+      </c>
+      <c r="D4" s="207" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="208" t="inlineStr">
+        <is>
+          <t>Steuersatz</t>
+        </is>
+      </c>
+      <c r="B5" s="209" t="inlineStr">
+        <is>
+          <t>30 %</t>
+        </is>
+      </c>
+      <c r="C5" s="210" t="inlineStr">
+        <is>
+          <t>Kurs-Template (baseline tax rate)</t>
+        </is>
+      </c>
+      <c r="D5" s="210" t="inlineStr">
+        <is>
+          <t>Vorgegeben; entspricht grob der dt. effektiven Unternehmenssteuer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="208" t="inlineStr">
+        <is>
+          <t>Risk-free (rf)</t>
+        </is>
+      </c>
+      <c r="B6" s="209" t="inlineStr">
+        <is>
+          <t>3,50 %</t>
+        </is>
+      </c>
+      <c r="C6" s="210" t="inlineStr">
+        <is>
+          <t>Dt. Bundesanleihe 30 Jahre, 30.06.2026 (Investing.com; Ø des Fensters 3,50 %)</t>
+        </is>
+      </c>
+      <c r="D6" s="210" t="inlineStr">
+        <is>
+          <t>30-jährig statt 10-jährig gewählt, weil die Laufzeit zum unendlichen Horizont der DCF / des Terminal Value passt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="208" t="inlineStr">
+        <is>
+          <t>Equity Market Premium</t>
+        </is>
+      </c>
+      <c r="B7" s="209" t="inlineStr">
+        <is>
+          <t>4,23 %</t>
+        </is>
+      </c>
+      <c r="C7" s="210" t="inlineStr">
+        <is>
+          <t>Kurs-Template (Deutschland)</t>
+        </is>
+      </c>
+      <c r="D7" s="210" t="inlineStr">
+        <is>
+          <t>Vorgegeben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="208" t="inlineStr">
+        <is>
+          <t>LT-Wachstum (g)</t>
+        </is>
+      </c>
+      <c r="B8" s="209" t="inlineStr">
+        <is>
+          <t>1,50 %</t>
+        </is>
+      </c>
+      <c r="C8" s="210" t="inlineStr">
+        <is>
+          <t>Eigene Annahme</t>
+        </is>
+      </c>
+      <c r="D8" s="210" t="inlineStr">
+        <is>
+          <t>Unter dem langfristigen BIP-Wachstum (Faustregel 1–3 %, DePamphilis 2014); konservativ für einen reifen, zyklischen Truck-Markt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="208" t="inlineStr">
+        <is>
+          <t>Umsatz 2026E / 2027E</t>
+        </is>
+      </c>
+      <c r="B9" s="209" t="inlineStr">
+        <is>
+          <t>45.897 / 48.970</t>
+        </is>
+      </c>
+      <c r="C9" s="210" t="inlineStr">
+        <is>
+          <t>Bloomberg-Konsens (8TRA GY)</t>
+        </is>
+      </c>
+      <c r="D9" s="210" t="inlineStr">
+        <is>
+          <t>Template erlaubt explizit Analysten-Forecasts; Konsens robuster als eigene Extrapolation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="208" t="inlineStr">
+        <is>
+          <t>Umsatzwachstum 2028E–2032E</t>
+        </is>
+      </c>
+      <c r="B10" s="209" t="inlineStr">
+        <is>
+          <t>5,0 % → 1,5 %</t>
+        </is>
+      </c>
+      <c r="C10" s="210" t="inlineStr">
+        <is>
+          <t>Eigene Annahme (lineares Fading)</t>
+        </is>
+      </c>
+      <c r="D10" s="210" t="inlineStr">
+        <is>
+          <t>Konvergenz vom Konsens-Niveau (2027E) zum Langfrist-Wachstum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="208" t="inlineStr">
+        <is>
+          <t>EBIT-Marge 2026E / 2027E</t>
+        </is>
+      </c>
+      <c r="B11" s="209" t="inlineStr">
+        <is>
+          <t>6,6 % / 8,1 %</t>
+        </is>
+      </c>
+      <c r="C11" s="210" t="inlineStr">
+        <is>
+          <t>Bloomberg-Konsens</t>
+        </is>
+      </c>
+      <c r="D11" s="210" t="inlineStr">
+        <is>
+          <t>Wie Umsatz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="208" t="inlineStr">
+        <is>
+          <t>EBIT-Marge 2028E–2032E</t>
+        </is>
+      </c>
+      <c r="B12" s="209" t="inlineStr">
+        <is>
+          <t>8,0 %</t>
+        </is>
+      </c>
+      <c r="C12" s="210" t="inlineStr">
+        <is>
+          <t>Eigene Annahme</t>
+        </is>
+      </c>
+      <c r="D12" s="210" t="inlineStr">
+        <is>
+          <t>Mid-Cycle-Marge; nahe Konsens 2027E, unter Tratons Zielmarge (~9 %) → konservativ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="208" t="inlineStr">
+        <is>
+          <t>D&amp;A / Umsatz</t>
+        </is>
+      </c>
+      <c r="B13" s="209" t="inlineStr">
+        <is>
+          <t>7,0 %</t>
+        </is>
+      </c>
+      <c r="C13" s="210" t="inlineStr">
+        <is>
+          <t>Historisch (2025: D&amp;A ≈ EBITDA − EBIT = 3.147 / 44.051 = 7,1 %)</t>
+        </is>
+      </c>
+      <c r="D13" s="210" t="inlineStr">
+        <is>
+          <t>Über den Zyklus stabil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="208" t="inlineStr">
+        <is>
+          <t>CapEx / Umsatz</t>
+        </is>
+      </c>
+      <c r="B14" s="209" t="inlineStr">
+        <is>
+          <t>7,0 %</t>
+        </is>
+      </c>
+      <c r="C14" s="210" t="inlineStr">
+        <is>
+          <t>Eigene Annahme (≈ D&amp;A)</t>
+        </is>
+      </c>
+      <c r="D14" s="210" t="inlineStr">
+        <is>
+          <t>Inkl. kapitalisierter Entwicklungskosten (Traton aktiviert erhebliche R&amp;D). Reine Sachinvestitionen ~3,6 %, Gesamtinvestition ≈ D&amp;A → Netto-Add-back ≈ 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="208" t="inlineStr">
+        <is>
+          <t>ΔNWC / Umsatz</t>
+        </is>
+      </c>
+      <c r="B15" s="209" t="inlineStr">
+        <is>
+          <t>1,6 %</t>
+        </is>
+      </c>
+      <c r="C15" s="210" t="inlineStr">
+        <is>
+          <t>Kalibriert</t>
+        </is>
+      </c>
+      <c r="D15" s="210" t="inlineStr">
+        <is>
+          <t>So gesetzt, dass der FCFF den Analysten-Konsens-FCF (~1,2–1,4 Mrd 2026E) trifft. Bildet den Cash-Drag des wachsenden Finanzierungsgeschäfts ab. Ein naiver NOPAT-FCFF (~2,1 Mrd) ignoriert diesen Drag und überschätzt den Wert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="206" t="inlineStr">
+        <is>
+          <t>B · WACC</t>
+        </is>
+      </c>
+      <c r="B17" s="204" t="n"/>
+      <c r="C17" s="204" t="n"/>
+      <c r="D17" s="205" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="207" t="inlineStr">
+        <is>
+          <t>Annahme</t>
+        </is>
+      </c>
+      <c r="B18" s="207" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="C18" s="207" t="inlineStr">
+        <is>
+          <t>Herleitung / Quelle</t>
+        </is>
+      </c>
+      <c r="D18" s="207" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="208" t="inlineStr">
+        <is>
+          <t>CDS-Spread</t>
+        </is>
+      </c>
+      <c r="B19" s="209" t="inlineStr">
+        <is>
+          <t>1,20 %</t>
+        </is>
+      </c>
+      <c r="C19" s="210" t="inlineStr">
+        <is>
+          <t>Eigene Annahme (Investment-Grade-Emittent)</t>
+        </is>
+      </c>
+      <c r="D19" s="210" t="inlineStr">
+        <is>
+          <t>Pre-tax Cost of Debt = rf + CDS-Spread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="208" t="inlineStr">
+        <is>
+          <t>Peer-Betas</t>
+        </is>
+      </c>
+      <c r="B20" s="209" t="inlineStr">
+        <is>
+          <t>Volvo 0,88 · Daimler 0,91</t>
+        </is>
+      </c>
+      <c r="C20" s="210" t="inlineStr">
+        <is>
+          <t>Investing.com (5-Jahr)</t>
+        </is>
+      </c>
+      <c r="D20" s="210" t="inlineStr">
+        <is>
+          <t>Tratons eigener Beta ist verzerrt (VW hält ~90 % → dünner Free Float) → Peer-Group-Ansatz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="208" t="inlineStr">
+        <is>
+          <t>Iveco-Beta (1,04)</t>
+        </is>
+      </c>
+      <c r="B21" s="209" t="inlineStr">
+        <is>
+          <t>ausgeschlossen</t>
+        </is>
+      </c>
+      <c r="C21" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="210" t="inlineStr">
+        <is>
+          <t>Iveco ist industriell net cash → Unlevering explodiert und verzerrt die Gruppe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="208" t="inlineStr">
+        <is>
+          <t>Unlevering-Basis</t>
+        </is>
+      </c>
+      <c r="B22" s="209" t="inlineStr">
+        <is>
+          <t>Industrielle Nettoschuld (EV − MCap)</t>
+        </is>
+      </c>
+      <c r="C22" s="210" t="inlineStr">
+        <is>
+          <t>Bloomberg-EV</t>
+        </is>
+      </c>
+      <c r="D22" s="210" t="inlineStr">
+        <is>
+          <t>Bruttoschuld enthält Captive-Finance-Schuld → würde den Beta verzerren (siehe A.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="208" t="inlineStr">
+        <is>
+          <t>Unlevered Peer-Beta</t>
+        </is>
+      </c>
+      <c r="B23" s="209" t="inlineStr">
+        <is>
+          <t>≈ 1,00</t>
+        </is>
+      </c>
+      <c r="C23" s="210" t="inlineStr">
+        <is>
+          <t>Ø(Daimler, Volvo unlevered)</t>
+        </is>
+      </c>
+      <c r="D23" s="210" t="inlineStr">
+        <is>
+          <t>βu = βL / (1 + (1−t)·D/E).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="208" t="inlineStr">
+        <is>
+          <t>Re-levered Beta</t>
+        </is>
+      </c>
+      <c r="B24" s="209" t="inlineStr">
+        <is>
+          <t>1,20</t>
+        </is>
+      </c>
+      <c r="C24" s="210" t="inlineStr">
+        <is>
+          <t>βu·(1+(1−t)·D/E); Traton ind. D/E = 4.539/16.590 = 0,27</t>
+        </is>
+      </c>
+      <c r="D24" s="210" t="inlineStr">
+        <is>
+          <t>Auf Tratons industrielle Kapitalstruktur angepasst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="208" t="inlineStr">
+        <is>
+          <t>Cost of Equity</t>
+        </is>
+      </c>
+      <c r="B25" s="209" t="inlineStr">
+        <is>
+          <t>8,57 %</t>
+        </is>
+      </c>
+      <c r="C25" s="210" t="inlineStr">
+        <is>
+          <t>CAPM: rf + β·ERP = 3,5 % + 1,20·4,23 %</t>
+        </is>
+      </c>
+      <c r="D25" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="208" t="inlineStr">
+        <is>
+          <t>After-tax Cost of Debt</t>
+        </is>
+      </c>
+      <c r="B26" s="209" t="inlineStr">
+        <is>
+          <t>3,29 %</t>
+        </is>
+      </c>
+      <c r="C26" s="210" t="inlineStr">
+        <is>
+          <t>(rf + CDS)·(1−t) = 4,7 %·0,7</t>
+        </is>
+      </c>
+      <c r="D26" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="208" t="inlineStr">
+        <is>
+          <t>Gewichte E/V · D/V</t>
+        </is>
+      </c>
+      <c r="B27" s="209" t="inlineStr">
+        <is>
+          <t>79 % · 21 %</t>
+        </is>
+      </c>
+      <c r="C27" s="210" t="inlineStr">
+        <is>
+          <t>Industriell: MCap 16.590 / ind. Nettoschuld 4.539</t>
+        </is>
+      </c>
+      <c r="D27" s="210" t="inlineStr">
+        <is>
+          <t>Captive-Finance-Schuld ausgeschlossen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="208" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B28" s="209" t="inlineStr">
+        <is>
+          <t>7,43 %</t>
+        </is>
+      </c>
+      <c r="C28" s="210" t="inlineStr">
+        <is>
+          <t>E/V·Re + D/V·Kd</t>
+        </is>
+      </c>
+      <c r="D28" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="206" t="inlineStr">
+        <is>
+          <t>C · Equity Bridge</t>
+        </is>
+      </c>
+      <c r="B30" s="204" t="n"/>
+      <c r="C30" s="204" t="n"/>
+      <c r="D30" s="205" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="207" t="inlineStr">
+        <is>
+          <t>Annahme</t>
+        </is>
+      </c>
+      <c r="B31" s="207" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="C31" s="207" t="inlineStr">
+        <is>
+          <t>Herleitung / Quelle</t>
+        </is>
+      </c>
+      <c r="D31" s="207" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="208" t="inlineStr">
+        <is>
+          <t>Industrielle Nettoschuld</t>
+        </is>
+      </c>
+      <c r="B32" s="209" t="inlineStr">
+        <is>
+          <t>4.539</t>
+        </is>
+      </c>
+      <c r="C32" s="210" t="inlineStr">
+        <is>
+          <t>EV (21.129) − MCap (16.590), Bloomberg</t>
+        </is>
+      </c>
+      <c r="D32" s="210" t="inlineStr">
+        <is>
+          <t>Captive-Finance-Schuld (~22 Mrd) via „Preferred &amp; Other" rausgerechnet. Bruttoschuld (28.799) wäre falsch (siehe A.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="208" t="inlineStr">
+        <is>
+          <t>Pensionen</t>
+        </is>
+      </c>
+      <c r="B33" s="209" t="inlineStr">
+        <is>
+          <t>1.590</t>
+        </is>
+      </c>
+      <c r="C33" s="210" t="inlineStr">
+        <is>
+          <t>Geschäftsbericht 2025, S. 210 (Netto-Defined-Benefit-Verpflichtung)</t>
+        </is>
+      </c>
+      <c r="D33" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="208" t="inlineStr">
+        <is>
+          <t>Minderheiten</t>
+        </is>
+      </c>
+      <c r="B34" s="209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C34" s="210" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D34" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="208" t="inlineStr">
+        <is>
+          <t>Aktien</t>
+        </is>
+      </c>
+      <c r="B35" s="209" t="inlineStr">
+        <is>
+          <t>500 Mio</t>
+        </is>
+      </c>
+      <c r="C35" s="210" t="inlineStr">
+        <is>
+          <t>Bloomberg / Geschäftsbericht</t>
+        </is>
+      </c>
+      <c r="D35" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="208" t="inlineStr">
+        <is>
+          <t>Aktueller Kurs</t>
+        </is>
+      </c>
+      <c r="B36" s="209" t="inlineStr">
+        <is>
+          <t>33,18 €</t>
+        </is>
+      </c>
+      <c r="C36" s="210" t="inlineStr">
+        <is>
+          <t>Kurshistorie 30.06.2026</t>
+        </is>
+      </c>
+      <c r="D36" s="210" t="inlineStr">
+        <is>
+          <t>Referenzpunkt für den Upside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="206" t="inlineStr">
+        <is>
+          <t>D · Multiples</t>
+        </is>
+      </c>
+      <c r="B38" s="204" t="n"/>
+      <c r="C38" s="204" t="n"/>
+      <c r="D38" s="205" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="207" t="inlineStr">
+        <is>
+          <t>Annahme</t>
+        </is>
+      </c>
+      <c r="B39" s="207" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="C39" s="207" t="inlineStr">
+        <is>
+          <t>Herleitung / Quelle</t>
+        </is>
+      </c>
+      <c r="D39" s="207" t="inlineStr">
+        <is>
+          <t>Begründung</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="208" t="inlineStr">
+        <is>
+          <t>Peer-Set</t>
+        </is>
+      </c>
+      <c r="B40" s="209" t="inlineStr">
+        <is>
+          <t>Daimler Truck, Volvo</t>
+        </is>
+      </c>
+      <c r="C40" s="210" t="inlineStr">
+        <is>
+          <t>Case-Vorgabe (Referenz + 2 Peers)</t>
+        </is>
+      </c>
+      <c r="D40" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="208" t="inlineStr">
+        <is>
+          <t>Perioden</t>
+        </is>
+      </c>
+      <c r="B41" s="209" t="inlineStr">
+        <is>
+          <t>LFY / LTM / FY+1 / FY+2</t>
+        </is>
+      </c>
+      <c r="C41" s="210" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D41" s="210" t="inlineStr">
+        <is>
+          <t>FY+1 = 2026E als Headline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="208" t="inlineStr">
+        <is>
+          <t>Währung Volvo</t>
+        </is>
+      </c>
+      <c r="B42" s="209" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="C42" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="210" t="inlineStr">
+        <is>
+          <t>Multiples sind Verhältnisse → währungsneutral; keine FX-Umrechnung nötig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="208" t="inlineStr">
+        <is>
+          <t>Impliziter EV</t>
+        </is>
+      </c>
+      <c r="B43" s="209" t="inlineStr">
+        <is>
+          <t>Median-Peer-Multiple × Traton-Kennzahl</t>
+        </is>
+      </c>
+      <c r="C43" s="210" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="210" t="inlineStr">
+        <is>
+          <t>Median robuster als Mittelwert bei nur 2 Peers mit großer Spreizung (Volvo Premium).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="211" t="inlineStr">
+        <is>
+          <t>Wichtigste Urteilsentscheidungen (vom Team getroffen):</t>
+        </is>
+      </c>
+      <c r="B45" s="204" t="n"/>
+      <c r="C45" s="204" t="n"/>
+      <c r="D45" s="205" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="212" t="inlineStr">
+        <is>
+          <t>(1) Industrielle Sicht statt konsolidiert — Captive-Finance-Schuld aus WACC &amp; Equity Bridge herausgerechnet (sonst WACC ~5 % und unsinniger +499 %-Upside).</t>
+        </is>
+      </c>
+      <c r="B46" s="204" t="n"/>
+      <c r="C46" s="204" t="n"/>
+      <c r="D46" s="205" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="212" t="inlineStr">
+        <is>
+          <t>(2) FCFF am Konsens-FCF verankert (nicht naiv NOPAT-basiert) — konservativer und bildet den Cash-Drag des Finanzierungsgeschäfts ab.</t>
+        </is>
+      </c>
+      <c r="B47" s="204" t="n"/>
+      <c r="C47" s="204" t="n"/>
+      <c r="D47" s="205" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A46:D46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="11" customWidth="1" style="196" min="1" max="1"/>
+    <col width="36.33203125" customWidth="1" style="196" min="2" max="2"/>
+    <col width="17.44140625" customWidth="1" style="196" min="3" max="6"/>
+    <col width="19.33203125" customWidth="1" style="196" min="7" max="7"/>
+    <col width="17.44140625" customWidth="1" style="196" min="8" max="22"/>
+    <col width="18.44140625" customWidth="1" style="196" min="23" max="23"/>
+    <col width="11" customWidth="1" style="196" min="24" max="24"/>
+    <col width="11" customWidth="1" style="196" min="25" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1780,7 +2804,7 @@
           <t>Tax rate:</t>
         </is>
       </c>
-      <c r="C3" s="207" t="n">
+      <c r="C3" s="213" t="n">
         <v>0.3</v>
       </c>
       <c r="D3" s="14" t="n"/>
@@ -1810,7 +2834,7 @@
           <t>LT growth rate</t>
         </is>
       </c>
-      <c r="C4" s="207" t="n">
+      <c r="C4" s="213" t="n">
         <v>0.015</v>
       </c>
       <c r="D4" s="14" t="n"/>
@@ -1840,7 +2864,7 @@
           <t>Revenue growth rate</t>
         </is>
       </c>
-      <c r="C5" s="207" t="n">
+      <c r="C5" s="213" t="n">
         <v>0.041</v>
       </c>
       <c r="D5" s="14" t="n"/>
@@ -1870,7 +2894,7 @@
           <t>COGS / Revenue</t>
         </is>
       </c>
-      <c r="C6" s="207" t="n">
+      <c r="C6" s="213" t="n">
         <v>0.805</v>
       </c>
       <c r="D6" s="14" t="n"/>
@@ -1900,7 +2924,7 @@
           <t>General Cost growth rate</t>
         </is>
       </c>
-      <c r="C7" s="207" t="n">
+      <c r="C7" s="213" t="n">
         <v>0.02</v>
       </c>
       <c r="D7" s="14" t="n"/>
@@ -1930,7 +2954,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="C8" s="207" t="n">
+      <c r="C8" s="213" t="n">
         <v>0.0743</v>
       </c>
       <c r="D8" s="14" t="n"/>
@@ -1960,7 +2984,7 @@
           <t>Annual Capex / Revenue</t>
         </is>
       </c>
-      <c r="C9" s="207" t="n">
+      <c r="C9" s="213" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="D9" s="14" t="n"/>
@@ -1990,7 +3014,7 @@
           <t>Avg delta NWC</t>
         </is>
       </c>
-      <c r="C10" s="207" t="n">
+      <c r="C10" s="213" t="n">
         <v>0.016</v>
       </c>
       <c r="D10" s="14" t="n"/>
@@ -2020,7 +3044,7 @@
           <t>Valuation date</t>
         </is>
       </c>
-      <c r="C11" s="183" t="n">
+      <c r="C11" s="177" t="n">
         <v>46203</v>
       </c>
       <c r="D11" s="14" t="n"/>
@@ -2074,22 +3098,22 @@
           <t>Assumptions (you can instead always use analyst FC)</t>
         </is>
       </c>
-      <c r="C13" s="55" t="n">
+      <c r="C13" s="53" t="n">
         <v>2021</v>
       </c>
-      <c r="D13" s="55" t="n">
+      <c r="D13" s="53" t="n">
         <v>2022</v>
       </c>
-      <c r="E13" s="55" t="n">
+      <c r="E13" s="53" t="n">
         <v>2023</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="53" t="n">
         <v>2024</v>
       </c>
-      <c r="G13" s="55" t="n">
+      <c r="G13" s="53" t="n">
         <v>2025</v>
       </c>
-      <c r="H13" s="56" t="inlineStr">
+      <c r="H13" s="54" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
@@ -2116,12 +3140,12 @@
           <t>Revenue growth rate (historical)</t>
         </is>
       </c>
-      <c r="C14" s="208" t="n"/>
-      <c r="D14" s="208" t="n"/>
-      <c r="E14" s="208" t="n"/>
-      <c r="F14" s="208" t="n"/>
-      <c r="G14" s="209" t="n"/>
-      <c r="H14" s="208" t="n"/>
+      <c r="C14" s="214" t="n"/>
+      <c r="D14" s="214" t="n"/>
+      <c r="E14" s="214" t="n"/>
+      <c r="F14" s="214" t="n"/>
+      <c r="G14" s="215" t="n"/>
+      <c r="H14" s="214" t="n"/>
       <c r="I14" s="14" t="n"/>
       <c r="J14" s="14" t="n"/>
       <c r="K14" s="14" t="n"/>
@@ -2144,12 +3168,12 @@
           <t>COGS / Revenue</t>
         </is>
       </c>
-      <c r="C15" s="208" t="n"/>
-      <c r="D15" s="208" t="n"/>
-      <c r="E15" s="208" t="n"/>
-      <c r="F15" s="208" t="n"/>
-      <c r="G15" s="210" t="n"/>
-      <c r="H15" s="208" t="n"/>
+      <c r="C15" s="214" t="n"/>
+      <c r="D15" s="214" t="n"/>
+      <c r="E15" s="214" t="n"/>
+      <c r="F15" s="214" t="n"/>
+      <c r="G15" s="216" t="n"/>
+      <c r="H15" s="214" t="n"/>
       <c r="I15" s="14" t="n"/>
       <c r="J15" s="14" t="n"/>
       <c r="K15" s="14" t="n"/>
@@ -2172,12 +3196,12 @@
           <t>COGS / Revenue growth rate</t>
         </is>
       </c>
-      <c r="C16" s="208" t="n"/>
-      <c r="D16" s="208" t="n"/>
-      <c r="E16" s="208" t="n"/>
-      <c r="F16" s="208" t="n"/>
-      <c r="G16" s="210" t="n"/>
-      <c r="H16" s="208" t="n"/>
+      <c r="C16" s="214" t="n"/>
+      <c r="D16" s="214" t="n"/>
+      <c r="E16" s="214" t="n"/>
+      <c r="F16" s="214" t="n"/>
+      <c r="G16" s="216" t="n"/>
+      <c r="H16" s="214" t="n"/>
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="14" t="n"/>
       <c r="K16" s="14" t="n"/>
@@ -2200,12 +3224,12 @@
           <t>SG&amp;A / Revenue</t>
         </is>
       </c>
-      <c r="C17" s="208" t="n"/>
-      <c r="D17" s="208" t="n"/>
-      <c r="E17" s="208" t="n"/>
-      <c r="F17" s="208" t="n"/>
-      <c r="G17" s="210" t="n"/>
-      <c r="H17" s="208" t="n"/>
+      <c r="C17" s="214" t="n"/>
+      <c r="D17" s="214" t="n"/>
+      <c r="E17" s="214" t="n"/>
+      <c r="F17" s="214" t="n"/>
+      <c r="G17" s="216" t="n"/>
+      <c r="H17" s="214" t="n"/>
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="14" t="n"/>
       <c r="K17" s="14" t="n"/>
@@ -2228,12 +3252,12 @@
           <t>CapEx / Revenue</t>
         </is>
       </c>
-      <c r="C18" s="208" t="n"/>
-      <c r="D18" s="208" t="n"/>
-      <c r="E18" s="208" t="n"/>
-      <c r="F18" s="208" t="n"/>
-      <c r="G18" s="210" t="n"/>
-      <c r="H18" s="208" t="n"/>
+      <c r="C18" s="214" t="n"/>
+      <c r="D18" s="214" t="n"/>
+      <c r="E18" s="214" t="n"/>
+      <c r="F18" s="214" t="n"/>
+      <c r="G18" s="216" t="n"/>
+      <c r="H18" s="214" t="n"/>
       <c r="I18" s="14" t="n"/>
       <c r="J18" s="14" t="n"/>
       <c r="K18" s="14" t="n"/>
@@ -2256,12 +3280,12 @@
           <t>Depreciation / Revenue</t>
         </is>
       </c>
-      <c r="C19" s="208" t="n"/>
-      <c r="D19" s="208" t="n"/>
-      <c r="E19" s="208" t="n"/>
-      <c r="F19" s="208" t="n"/>
-      <c r="G19" s="210" t="n"/>
-      <c r="H19" s="208" t="n"/>
+      <c r="C19" s="214" t="n"/>
+      <c r="D19" s="214" t="n"/>
+      <c r="E19" s="214" t="n"/>
+      <c r="F19" s="214" t="n"/>
+      <c r="G19" s="216" t="n"/>
+      <c r="H19" s="214" t="n"/>
       <c r="I19" s="14" t="n"/>
       <c r="J19" s="14" t="n"/>
       <c r="K19" s="14" t="n"/>
@@ -2284,12 +3308,12 @@
           <t>Depreciation / CapEx</t>
         </is>
       </c>
-      <c r="C20" s="208" t="n"/>
-      <c r="D20" s="208" t="n"/>
-      <c r="E20" s="208" t="n"/>
-      <c r="F20" s="208" t="n"/>
-      <c r="G20" s="210" t="n"/>
-      <c r="H20" s="208" t="n"/>
+      <c r="C20" s="214" t="n"/>
+      <c r="D20" s="214" t="n"/>
+      <c r="E20" s="214" t="n"/>
+      <c r="F20" s="214" t="n"/>
+      <c r="G20" s="216" t="n"/>
+      <c r="H20" s="214" t="n"/>
       <c r="I20" s="14" t="n"/>
       <c r="J20" s="14" t="n"/>
       <c r="K20" s="14" t="n"/>
@@ -2312,12 +3336,12 @@
           <t>delta NWC / Revenue</t>
         </is>
       </c>
-      <c r="C21" s="208" t="n"/>
-      <c r="D21" s="208" t="n"/>
-      <c r="E21" s="208" t="n"/>
-      <c r="F21" s="208" t="n"/>
-      <c r="G21" s="210" t="n"/>
-      <c r="H21" s="208" t="n"/>
+      <c r="C21" s="214" t="n"/>
+      <c r="D21" s="214" t="n"/>
+      <c r="E21" s="214" t="n"/>
+      <c r="F21" s="214" t="n"/>
+      <c r="G21" s="216" t="n"/>
+      <c r="H21" s="214" t="n"/>
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="14" t="n"/>
       <c r="K21" s="14" t="n"/>
@@ -2393,7 +3417,7 @@
       <c r="H24" s="14" t="n"/>
       <c r="I24" s="14" t="n"/>
       <c r="J24" s="14" t="n"/>
-      <c r="K24" s="137" t="inlineStr">
+      <c r="K24" s="132" t="inlineStr">
         <is>
           <t>Forecast</t>
         </is>
@@ -2402,7 +3426,7 @@
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
       <c r="O24" s="14" t="n"/>
-      <c r="P24" s="58" t="inlineStr">
+      <c r="P24" s="56" t="inlineStr">
         <is>
           <t>TV</t>
         </is>
@@ -2413,7 +3437,7 @@
       <c r="T24" s="14" t="n"/>
       <c r="U24" s="14" t="n"/>
       <c r="V24" s="14" t="n"/>
-      <c r="W24" s="58" t="n"/>
+      <c r="W24" s="56" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="14" t="inlineStr">
@@ -2447,12 +3471,12 @@
       <c r="N25" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="O25" s="136" t="inlineStr">
+      <c r="O25" s="131" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="P25" s="136" t="inlineStr">
+      <c r="P25" s="131" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2471,58 +3495,58 @@
           <t>year</t>
         </is>
       </c>
-      <c r="C26" s="57" t="n">
+      <c r="C26" s="55" t="n">
         <v>2021</v>
       </c>
-      <c r="D26" s="57" t="n">
+      <c r="D26" s="55" t="n">
         <v>2022</v>
       </c>
-      <c r="E26" s="57" t="n">
+      <c r="E26" s="55" t="n">
         <v>2023</v>
       </c>
-      <c r="F26" s="57" t="n">
+      <c r="F26" s="55" t="n">
         <v>2024</v>
       </c>
-      <c r="G26" s="57" t="n">
+      <c r="G26" s="55" t="n">
         <v>2025</v>
       </c>
-      <c r="H26" s="74" t="inlineStr">
+      <c r="H26" s="71" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="I26" s="57" t="inlineStr">
+      <c r="I26" s="55" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="J26" s="57" t="inlineStr">
+      <c r="J26" s="55" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="K26" s="57" t="inlineStr">
+      <c r="K26" s="55" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="L26" s="57" t="inlineStr">
+      <c r="L26" s="55" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
       </c>
-      <c r="M26" s="57" t="inlineStr">
+      <c r="M26" s="55" t="inlineStr">
         <is>
           <t>2031E</t>
         </is>
       </c>
-      <c r="N26" s="57" t="inlineStr">
+      <c r="N26" s="55" t="inlineStr">
         <is>
           <t>2032E</t>
         </is>
       </c>
-      <c r="O26" s="57" t="n"/>
-      <c r="P26" s="138" t="inlineStr">
+      <c r="O26" s="55" t="n"/>
+      <c r="P26" s="133" t="inlineStr">
         <is>
           <t>TV</t>
         </is>
@@ -2534,44 +3558,44 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C27" s="211" t="n">
+      <c r="C27" s="217" t="n">
         <v>30620</v>
       </c>
-      <c r="D27" s="211" t="n">
+      <c r="D27" s="217" t="n">
         <v>40335</v>
       </c>
-      <c r="E27" s="211" t="n">
+      <c r="E27" s="217" t="n">
         <v>46872</v>
       </c>
-      <c r="F27" s="211" t="n">
+      <c r="F27" s="217" t="n">
         <v>47473</v>
       </c>
-      <c r="G27" s="212" t="n">
+      <c r="G27" s="218" t="n">
         <v>44051</v>
       </c>
-      <c r="H27" s="211" t="n">
+      <c r="H27" s="217" t="n">
         <v>45897</v>
       </c>
-      <c r="I27" s="211" t="n">
+      <c r="I27" s="217" t="n">
         <v>48970</v>
       </c>
-      <c r="J27" s="211" t="n">
+      <c r="J27" s="217" t="n">
         <v>51418</v>
       </c>
-      <c r="K27" s="211" t="n">
+      <c r="K27" s="217" t="n">
         <v>53218</v>
       </c>
-      <c r="L27" s="211" t="n">
+      <c r="L27" s="217" t="n">
         <v>54549</v>
       </c>
-      <c r="M27" s="211" t="n">
+      <c r="M27" s="217" t="n">
         <v>55640</v>
       </c>
-      <c r="N27" s="211" t="n">
+      <c r="N27" s="217" t="n">
         <v>56474</v>
       </c>
-      <c r="O27" s="211" t="n"/>
-      <c r="P27" s="211" t="n"/>
+      <c r="O27" s="217" t="n"/>
+      <c r="P27" s="217" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="14" t="inlineStr">
@@ -2579,41 +3603,41 @@
           <t>Revenue Growth (in %)</t>
         </is>
       </c>
-      <c r="C28" s="213" t="n"/>
-      <c r="D28" s="208" t="n"/>
-      <c r="E28" s="208" t="n"/>
-      <c r="F28" s="208" t="n"/>
-      <c r="G28" s="210" t="n"/>
-      <c r="H28" s="208">
+      <c r="C28" s="219" t="n"/>
+      <c r="D28" s="214" t="n"/>
+      <c r="E28" s="214" t="n"/>
+      <c r="F28" s="214" t="n"/>
+      <c r="G28" s="216" t="n"/>
+      <c r="H28" s="214">
         <f>H27/G27-1</f>
         <v/>
       </c>
-      <c r="I28" s="208">
+      <c r="I28" s="214">
         <f>I27/H27-1</f>
         <v/>
       </c>
-      <c r="J28" s="208">
+      <c r="J28" s="214">
         <f>J27/I27-1</f>
         <v/>
       </c>
-      <c r="K28" s="208">
+      <c r="K28" s="214">
         <f>K27/J27-1</f>
         <v/>
       </c>
-      <c r="L28" s="208">
+      <c r="L28" s="214">
         <f>L27/K27-1</f>
         <v/>
       </c>
-      <c r="M28" s="208">
+      <c r="M28" s="214">
         <f>M27/L27-1</f>
         <v/>
       </c>
-      <c r="N28" s="208">
+      <c r="N28" s="214">
         <f>N27/M27-1</f>
         <v/>
       </c>
-      <c r="O28" s="208" t="n"/>
-      <c r="P28" s="208" t="n"/>
+      <c r="O28" s="214" t="n"/>
+      <c r="P28" s="214" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="41" t="inlineStr">
@@ -2621,34 +3645,34 @@
           <t>COGS</t>
         </is>
       </c>
-      <c r="C29" s="214" t="n"/>
-      <c r="D29" s="214" t="n"/>
-      <c r="E29" s="214" t="n"/>
-      <c r="F29" s="214" t="n"/>
-      <c r="G29" s="214" t="n"/>
-      <c r="H29" s="215" t="n">
+      <c r="C29" s="220" t="n"/>
+      <c r="D29" s="220" t="n"/>
+      <c r="E29" s="220" t="n"/>
+      <c r="F29" s="220" t="n"/>
+      <c r="G29" s="220" t="n"/>
+      <c r="H29" s="221" t="n">
         <v>36947.1</v>
       </c>
-      <c r="I29" s="214" t="n">
+      <c r="I29" s="220" t="n">
         <v>39420.8</v>
       </c>
-      <c r="J29" s="214" t="n">
+      <c r="J29" s="220" t="n">
         <v>41391.5</v>
       </c>
-      <c r="K29" s="214" t="n">
+      <c r="K29" s="220" t="n">
         <v>42840.5</v>
       </c>
-      <c r="L29" s="214" t="n">
+      <c r="L29" s="220" t="n">
         <v>43911.9</v>
       </c>
-      <c r="M29" s="214" t="n">
+      <c r="M29" s="220" t="n">
         <v>44790.2</v>
       </c>
-      <c r="N29" s="214" t="n">
+      <c r="N29" s="220" t="n">
         <v>45461.6</v>
       </c>
-      <c r="O29" s="214" t="n"/>
-      <c r="P29" s="214" t="n"/>
+      <c r="O29" s="220" t="n"/>
+      <c r="P29" s="220" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="12" t="inlineStr">
@@ -2656,41 +3680,41 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C30" s="211" t="n"/>
-      <c r="D30" s="211" t="n"/>
-      <c r="E30" s="211" t="n"/>
-      <c r="F30" s="211" t="n"/>
-      <c r="G30" s="211" t="n"/>
-      <c r="H30" s="216">
+      <c r="C30" s="217" t="n"/>
+      <c r="D30" s="217" t="n"/>
+      <c r="E30" s="217" t="n"/>
+      <c r="F30" s="217" t="n"/>
+      <c r="G30" s="217" t="n"/>
+      <c r="H30" s="222">
         <f>H27-H29</f>
         <v/>
       </c>
-      <c r="I30" s="211">
+      <c r="I30" s="217">
         <f>I27-I29</f>
         <v/>
       </c>
-      <c r="J30" s="211">
+      <c r="J30" s="217">
         <f>J27-J29</f>
         <v/>
       </c>
-      <c r="K30" s="211">
+      <c r="K30" s="217">
         <f>K27-K29</f>
         <v/>
       </c>
-      <c r="L30" s="211">
+      <c r="L30" s="217">
         <f>L27-L29</f>
         <v/>
       </c>
-      <c r="M30" s="211">
+      <c r="M30" s="217">
         <f>M27-M29</f>
         <v/>
       </c>
-      <c r="N30" s="211">
+      <c r="N30" s="217">
         <f>N27-N29</f>
         <v/>
       </c>
-      <c r="O30" s="211" t="n"/>
-      <c r="P30" s="211" t="n"/>
+      <c r="O30" s="217" t="n"/>
+      <c r="P30" s="217" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="12" t="inlineStr">
@@ -2698,41 +3722,41 @@
           <t>Gross Profit as % of Revenue</t>
         </is>
       </c>
-      <c r="C31" s="208" t="n"/>
-      <c r="D31" s="208" t="n"/>
-      <c r="E31" s="208" t="n"/>
-      <c r="F31" s="208" t="n"/>
-      <c r="G31" s="208" t="n"/>
-      <c r="H31" s="213">
+      <c r="C31" s="214" t="n"/>
+      <c r="D31" s="214" t="n"/>
+      <c r="E31" s="214" t="n"/>
+      <c r="F31" s="214" t="n"/>
+      <c r="G31" s="214" t="n"/>
+      <c r="H31" s="219">
         <f>H30/H27</f>
         <v/>
       </c>
-      <c r="I31" s="208">
+      <c r="I31" s="214">
         <f>I30/I27</f>
         <v/>
       </c>
-      <c r="J31" s="208">
+      <c r="J31" s="214">
         <f>J30/J27</f>
         <v/>
       </c>
-      <c r="K31" s="208">
+      <c r="K31" s="214">
         <f>K30/K27</f>
         <v/>
       </c>
-      <c r="L31" s="208">
+      <c r="L31" s="214">
         <f>L30/L27</f>
         <v/>
       </c>
-      <c r="M31" s="208">
+      <c r="M31" s="214">
         <f>M30/M27</f>
         <v/>
       </c>
-      <c r="N31" s="208">
+      <c r="N31" s="214">
         <f>N30/N27</f>
         <v/>
       </c>
-      <c r="O31" s="46" t="n"/>
-      <c r="P31" s="46" t="n"/>
+      <c r="O31" s="45" t="n"/>
+      <c r="P31" s="45" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="41" t="inlineStr">
@@ -2740,167 +3764,128 @@
           <t>SG&amp;A</t>
         </is>
       </c>
-      <c r="C32" s="214" t="n"/>
-      <c r="D32" s="214" t="n"/>
-      <c r="E32" s="214" t="n"/>
-      <c r="F32" s="214" t="n"/>
-      <c r="G32" s="214" t="n"/>
-      <c r="H32" s="215" t="n">
+      <c r="C32" s="220" t="n"/>
+      <c r="D32" s="220" t="n"/>
+      <c r="E32" s="220" t="n"/>
+      <c r="F32" s="220" t="n"/>
+      <c r="G32" s="220" t="n"/>
+      <c r="H32" s="221" t="n">
         <v>2689.1</v>
       </c>
-      <c r="I32" s="214" t="n">
+      <c r="I32" s="220" t="n">
         <v>2135.2</v>
       </c>
-      <c r="J32" s="214" t="n">
+      <c r="J32" s="220" t="n">
         <v>2314.2</v>
       </c>
-      <c r="K32" s="214" t="n">
+      <c r="K32" s="220" t="n">
         <v>2395.2</v>
       </c>
-      <c r="L32" s="214" t="n">
+      <c r="L32" s="220" t="n">
         <v>2454.6</v>
       </c>
-      <c r="M32" s="214" t="n">
+      <c r="M32" s="220" t="n">
         <v>2504</v>
       </c>
-      <c r="N32" s="214" t="n">
+      <c r="N32" s="220" t="n">
         <v>2541.2</v>
       </c>
-      <c r="O32" s="214" t="n"/>
-      <c r="P32" s="214" t="n"/>
+      <c r="O32" s="220" t="n"/>
+      <c r="P32" s="220" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="59" t="inlineStr">
+      <c r="B33" s="57" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C33" s="217" t="n">
+      <c r="C33" s="223" t="n">
         <v>3231</v>
       </c>
-      <c r="D33" s="217" t="n">
+      <c r="D33" s="223" t="n">
         <v>4902</v>
       </c>
-      <c r="E33" s="217" t="n">
+      <c r="E33" s="223" t="n">
         <v>6686</v>
       </c>
-      <c r="F33" s="217" t="n">
+      <c r="F33" s="223" t="n">
         <v>7392</v>
       </c>
-      <c r="G33" s="217" t="n">
+      <c r="G33" s="223" t="n">
         <v>5966</v>
       </c>
-      <c r="H33" s="218">
+      <c r="H33" s="224">
         <f>H30-H32</f>
         <v/>
       </c>
-      <c r="I33" s="217">
+      <c r="I33" s="223">
         <f>I30-I32</f>
         <v/>
       </c>
-      <c r="J33" s="217">
+      <c r="J33" s="223">
         <f>J30-J32</f>
         <v/>
       </c>
-      <c r="K33" s="217">
+      <c r="K33" s="223">
         <f>K30-K32</f>
         <v/>
       </c>
-      <c r="L33" s="217">
+      <c r="L33" s="223">
         <f>L30-L32</f>
         <v/>
       </c>
-      <c r="M33" s="217">
+      <c r="M33" s="223">
         <f>M30-M32</f>
         <v/>
       </c>
-      <c r="N33" s="217">
+      <c r="N33" s="223">
         <f>N30-N32</f>
         <v/>
       </c>
-      <c r="O33" s="217" t="n"/>
-      <c r="P33" s="217" t="n"/>
+      <c r="O33" s="223" t="n"/>
+      <c r="P33" s="223" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n"/>
-      <c r="B34" s="140" t="inlineStr">
+      <c r="B34" s="135" t="inlineStr">
         <is>
           <t>EBITDA % margin</t>
         </is>
       </c>
-      <c r="C34" s="219" t="n"/>
-      <c r="D34" s="219" t="n"/>
-      <c r="E34" s="219" t="n"/>
-      <c r="F34" s="219" t="n"/>
-      <c r="G34" s="219" t="n"/>
-      <c r="H34" s="220">
+      <c r="C34" s="225" t="n"/>
+      <c r="D34" s="225" t="n"/>
+      <c r="E34" s="225" t="n"/>
+      <c r="F34" s="225" t="n"/>
+      <c r="G34" s="225" t="n"/>
+      <c r="H34" s="226">
         <f>H33/H27</f>
         <v/>
       </c>
-      <c r="I34" s="219">
+      <c r="I34" s="225">
         <f>I33/I27</f>
         <v/>
       </c>
-      <c r="J34" s="219">
+      <c r="J34" s="225">
         <f>J33/J27</f>
         <v/>
       </c>
-      <c r="K34" s="219">
+      <c r="K34" s="225">
         <f>K33/K27</f>
         <v/>
       </c>
-      <c r="L34" s="219">
+      <c r="L34" s="225">
         <f>L33/L27</f>
         <v/>
       </c>
-      <c r="M34" s="219">
+      <c r="M34" s="225">
         <f>M33/M27</f>
         <v/>
       </c>
-      <c r="N34" s="219">
+      <c r="N34" s="225">
         <f>N33/N27</f>
         <v/>
       </c>
-      <c r="O34" s="221" t="n"/>
-      <c r="P34" s="221" t="n"/>
-      <c r="Q34" s="1" t="n"/>
-      <c r="R34" s="1" t="n"/>
-      <c r="S34" s="1" t="n"/>
-      <c r="T34" s="1" t="n"/>
-      <c r="U34" s="1" t="n"/>
-      <c r="V34" s="1" t="n"/>
-      <c r="W34" s="1" t="n"/>
-      <c r="X34" s="1" t="n"/>
-      <c r="Y34" s="1" t="n"/>
-      <c r="Z34" s="1" t="n"/>
-      <c r="AA34" s="1" t="n"/>
-      <c r="AB34" s="1" t="n"/>
-      <c r="AC34" s="1" t="n"/>
-      <c r="AD34" s="1" t="n"/>
-      <c r="AE34" s="1" t="n"/>
-      <c r="AF34" s="1" t="n"/>
-      <c r="AG34" s="1" t="n"/>
-      <c r="AH34" s="1" t="n"/>
-      <c r="AI34" s="1" t="n"/>
-      <c r="AJ34" s="1" t="n"/>
-      <c r="AK34" s="1" t="n"/>
-      <c r="AL34" s="1" t="n"/>
-      <c r="AM34" s="1" t="n"/>
-      <c r="AN34" s="1" t="n"/>
-      <c r="AO34" s="1" t="n"/>
-      <c r="AP34" s="1" t="n"/>
-      <c r="AQ34" s="1" t="n"/>
-      <c r="AR34" s="1" t="n"/>
-      <c r="AS34" s="1" t="n"/>
-      <c r="AT34" s="1" t="n"/>
-      <c r="AU34" s="1" t="n"/>
-      <c r="AV34" s="1" t="n"/>
-      <c r="AW34" s="1" t="n"/>
-      <c r="AX34" s="1" t="n"/>
-      <c r="AY34" s="1" t="n"/>
-      <c r="AZ34" s="1" t="n"/>
-      <c r="BA34" s="1" t="n"/>
-      <c r="BB34" s="1" t="n"/>
+      <c r="O34" s="227" t="n"/>
+      <c r="P34" s="227" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="41" t="inlineStr">
@@ -2908,131 +3893,131 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="C35" s="214" t="n">
+      <c r="C35" s="220" t="n">
         <v>2729</v>
       </c>
-      <c r="D35" s="214" t="n">
+      <c r="D35" s="220" t="n">
         <v>2982</v>
       </c>
-      <c r="E35" s="214" t="n">
+      <c r="E35" s="220" t="n">
         <v>2861</v>
       </c>
-      <c r="F35" s="214" t="n">
+      <c r="F35" s="220" t="n">
         <v>2975</v>
       </c>
-      <c r="G35" s="214" t="n">
+      <c r="G35" s="220" t="n">
         <v>3147</v>
       </c>
-      <c r="H35" s="215" t="n">
+      <c r="H35" s="221" t="n">
         <v>3212.8</v>
       </c>
-      <c r="I35" s="214" t="n">
+      <c r="I35" s="220" t="n">
         <v>3427.9</v>
       </c>
-      <c r="J35" s="214" t="n">
+      <c r="J35" s="220" t="n">
         <v>3599.3</v>
       </c>
-      <c r="K35" s="214" t="n">
+      <c r="K35" s="220" t="n">
         <v>3725.3</v>
       </c>
-      <c r="L35" s="214" t="n">
+      <c r="L35" s="220" t="n">
         <v>3818.4</v>
       </c>
-      <c r="M35" s="214" t="n">
+      <c r="M35" s="220" t="n">
         <v>3894.8</v>
       </c>
-      <c r="N35" s="214" t="n">
+      <c r="N35" s="220" t="n">
         <v>3953.2</v>
       </c>
-      <c r="O35" s="214" t="n"/>
-      <c r="P35" s="214" t="n"/>
+      <c r="O35" s="220" t="n"/>
+      <c r="P35" s="220" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="59" t="inlineStr">
+      <c r="B36" s="57" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C36" s="217" t="n">
+      <c r="C36" s="223" t="n">
         <v>502</v>
       </c>
-      <c r="D36" s="217" t="n">
+      <c r="D36" s="223" t="n">
         <v>1920</v>
       </c>
-      <c r="E36" s="217" t="n">
+      <c r="E36" s="223" t="n">
         <v>3825</v>
       </c>
-      <c r="F36" s="217" t="n">
+      <c r="F36" s="223" t="n">
         <v>4417</v>
       </c>
-      <c r="G36" s="217" t="n">
+      <c r="G36" s="223" t="n">
         <v>2819</v>
       </c>
-      <c r="H36" s="218" t="n">
+      <c r="H36" s="224" t="n">
         <v>3048</v>
       </c>
-      <c r="I36" s="217" t="n">
+      <c r="I36" s="223" t="n">
         <v>3986</v>
       </c>
-      <c r="J36" s="217" t="n">
+      <c r="J36" s="223" t="n">
         <v>4113</v>
       </c>
-      <c r="K36" s="217" t="n">
+      <c r="K36" s="223" t="n">
         <v>4257</v>
       </c>
-      <c r="L36" s="217" t="n">
+      <c r="L36" s="223" t="n">
         <v>4364</v>
       </c>
-      <c r="M36" s="217" t="n">
+      <c r="M36" s="223" t="n">
         <v>4451</v>
       </c>
-      <c r="N36" s="217" t="n">
+      <c r="N36" s="223" t="n">
         <v>4518</v>
       </c>
-      <c r="O36" s="217" t="n"/>
-      <c r="P36" s="217" t="n"/>
+      <c r="O36" s="223" t="n"/>
+      <c r="P36" s="223" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="140" t="inlineStr">
+      <c r="B37" s="135" t="inlineStr">
         <is>
           <t>EBIT % margin</t>
         </is>
       </c>
-      <c r="C37" s="219" t="n"/>
-      <c r="D37" s="219" t="n"/>
-      <c r="E37" s="219" t="n"/>
-      <c r="F37" s="219" t="n"/>
-      <c r="G37" s="219" t="n"/>
-      <c r="H37" s="220">
+      <c r="C37" s="225" t="n"/>
+      <c r="D37" s="225" t="n"/>
+      <c r="E37" s="225" t="n"/>
+      <c r="F37" s="225" t="n"/>
+      <c r="G37" s="225" t="n"/>
+      <c r="H37" s="226">
         <f>H36/H27</f>
         <v/>
       </c>
-      <c r="I37" s="219">
+      <c r="I37" s="225">
         <f>I36/I27</f>
         <v/>
       </c>
-      <c r="J37" s="219">
+      <c r="J37" s="225">
         <f>J36/J27</f>
         <v/>
       </c>
-      <c r="K37" s="219">
+      <c r="K37" s="225">
         <f>K36/K27</f>
         <v/>
       </c>
-      <c r="L37" s="219">
+      <c r="L37" s="225">
         <f>L36/L27</f>
         <v/>
       </c>
-      <c r="M37" s="219">
+      <c r="M37" s="225">
         <f>M36/M27</f>
         <v/>
       </c>
-      <c r="N37" s="219">
+      <c r="N37" s="225">
         <f>N36/N27</f>
         <v/>
       </c>
-      <c r="O37" s="221" t="n"/>
-      <c r="P37" s="221" t="n"/>
+      <c r="O37" s="227" t="n"/>
+      <c r="P37" s="227" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="12" t="inlineStr">
@@ -3040,83 +4025,83 @@
           <t>Taxes paid</t>
         </is>
       </c>
-      <c r="C38" s="211" t="n"/>
-      <c r="D38" s="211" t="n"/>
-      <c r="E38" s="211" t="n"/>
-      <c r="F38" s="211" t="n"/>
-      <c r="G38" s="211" t="n"/>
-      <c r="H38" s="215">
+      <c r="C38" s="217" t="n"/>
+      <c r="D38" s="217" t="n"/>
+      <c r="E38" s="217" t="n"/>
+      <c r="F38" s="217" t="n"/>
+      <c r="G38" s="217" t="n"/>
+      <c r="H38" s="221">
         <f>H36*$C$3</f>
         <v/>
       </c>
-      <c r="I38" s="214">
+      <c r="I38" s="220">
         <f>I36*$C$3</f>
         <v/>
       </c>
-      <c r="J38" s="214">
+      <c r="J38" s="220">
         <f>J36*$C$3</f>
         <v/>
       </c>
-      <c r="K38" s="214">
+      <c r="K38" s="220">
         <f>K36*$C$3</f>
         <v/>
       </c>
-      <c r="L38" s="214">
+      <c r="L38" s="220">
         <f>L36*$C$3</f>
         <v/>
       </c>
-      <c r="M38" s="214">
+      <c r="M38" s="220">
         <f>M36*$C$3</f>
         <v/>
       </c>
-      <c r="N38" s="214">
+      <c r="N38" s="220">
         <f>N36*$C$3</f>
         <v/>
       </c>
-      <c r="O38" s="211" t="n"/>
-      <c r="P38" s="211" t="n"/>
+      <c r="O38" s="217" t="n"/>
+      <c r="P38" s="217" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="59" t="inlineStr">
+      <c r="B39" s="57" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C39" s="222" t="n"/>
-      <c r="D39" s="223" t="n"/>
-      <c r="E39" s="223" t="n"/>
-      <c r="F39" s="223" t="n"/>
-      <c r="G39" s="224" t="n"/>
-      <c r="H39" s="218">
+      <c r="C39" s="228" t="n"/>
+      <c r="D39" s="229" t="n"/>
+      <c r="E39" s="229" t="n"/>
+      <c r="F39" s="229" t="n"/>
+      <c r="G39" s="230" t="n"/>
+      <c r="H39" s="224">
         <f>H36-H38</f>
         <v/>
       </c>
-      <c r="I39" s="217">
+      <c r="I39" s="223">
         <f>I36-I38</f>
         <v/>
       </c>
-      <c r="J39" s="217">
+      <c r="J39" s="223">
         <f>J36-J38</f>
         <v/>
       </c>
-      <c r="K39" s="217">
+      <c r="K39" s="223">
         <f>K36-K38</f>
         <v/>
       </c>
-      <c r="L39" s="217">
+      <c r="L39" s="223">
         <f>L36-L38</f>
         <v/>
       </c>
-      <c r="M39" s="217">
+      <c r="M39" s="223">
         <f>M36-M38</f>
         <v/>
       </c>
-      <c r="N39" s="217">
+      <c r="N39" s="223">
         <f>N36-N38</f>
         <v/>
       </c>
-      <c r="O39" s="223" t="n"/>
-      <c r="P39" s="223" t="n"/>
+      <c r="O39" s="229" t="n"/>
+      <c r="P39" s="229" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="12" t="inlineStr">
@@ -3124,44 +4109,44 @@
           <t>CapEx</t>
         </is>
       </c>
-      <c r="C40" s="211" t="n">
+      <c r="C40" s="217" t="n">
         <v>1131</v>
       </c>
-      <c r="D40" s="211" t="n">
+      <c r="D40" s="217" t="n">
         <v>1305</v>
       </c>
-      <c r="E40" s="211" t="n">
+      <c r="E40" s="217" t="n">
         <v>1522</v>
       </c>
-      <c r="F40" s="211" t="n">
+      <c r="F40" s="217" t="n">
         <v>1763</v>
       </c>
-      <c r="G40" s="211" t="n">
+      <c r="G40" s="217" t="n">
         <v>1576</v>
       </c>
-      <c r="H40" s="216" t="n">
+      <c r="H40" s="222" t="n">
         <v>3212.8</v>
       </c>
-      <c r="I40" s="211" t="n">
+      <c r="I40" s="217" t="n">
         <v>3427.9</v>
       </c>
-      <c r="J40" s="211" t="n">
+      <c r="J40" s="217" t="n">
         <v>3599.3</v>
       </c>
-      <c r="K40" s="211" t="n">
+      <c r="K40" s="217" t="n">
         <v>3725.3</v>
       </c>
-      <c r="L40" s="211" t="n">
+      <c r="L40" s="217" t="n">
         <v>3818.4</v>
       </c>
-      <c r="M40" s="211" t="n">
+      <c r="M40" s="217" t="n">
         <v>3894.8</v>
       </c>
-      <c r="N40" s="211" t="n">
+      <c r="N40" s="217" t="n">
         <v>3953.2</v>
       </c>
-      <c r="O40" s="211" t="n"/>
-      <c r="P40" s="211" t="n"/>
+      <c r="O40" s="217" t="n"/>
+      <c r="P40" s="217" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="12" t="inlineStr">
@@ -3169,44 +4154,44 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="C41" s="211" t="n">
+      <c r="C41" s="217" t="n">
         <v>2729</v>
       </c>
-      <c r="D41" s="211" t="n">
+      <c r="D41" s="217" t="n">
         <v>2982</v>
       </c>
-      <c r="E41" s="211" t="n">
+      <c r="E41" s="217" t="n">
         <v>2861</v>
       </c>
-      <c r="F41" s="211" t="n">
+      <c r="F41" s="217" t="n">
         <v>2975</v>
       </c>
-      <c r="G41" s="211" t="n">
+      <c r="G41" s="217" t="n">
         <v>3147</v>
       </c>
-      <c r="H41" s="216" t="n">
+      <c r="H41" s="222" t="n">
         <v>3212.8</v>
       </c>
-      <c r="I41" s="211" t="n">
+      <c r="I41" s="217" t="n">
         <v>3427.9</v>
       </c>
-      <c r="J41" s="211" t="n">
+      <c r="J41" s="217" t="n">
         <v>3599.3</v>
       </c>
-      <c r="K41" s="211" t="n">
+      <c r="K41" s="217" t="n">
         <v>3725.3</v>
       </c>
-      <c r="L41" s="211" t="n">
+      <c r="L41" s="217" t="n">
         <v>3818.4</v>
       </c>
-      <c r="M41" s="211" t="n">
+      <c r="M41" s="217" t="n">
         <v>3894.8</v>
       </c>
-      <c r="N41" s="211" t="n">
+      <c r="N41" s="217" t="n">
         <v>3953.2</v>
       </c>
-      <c r="O41" s="211" t="n"/>
-      <c r="P41" s="211" t="n"/>
+      <c r="O41" s="217" t="n"/>
+      <c r="P41" s="217" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="12" t="inlineStr">
@@ -3214,76 +4199,76 @@
           <t>delta Net Working Capital</t>
         </is>
       </c>
-      <c r="C42" s="211" t="n"/>
-      <c r="D42" s="211" t="n"/>
-      <c r="E42" s="211" t="n"/>
-      <c r="F42" s="211" t="n"/>
-      <c r="G42" s="211" t="n"/>
-      <c r="H42" s="216" t="n">
+      <c r="C42" s="217" t="n"/>
+      <c r="D42" s="217" t="n"/>
+      <c r="E42" s="217" t="n"/>
+      <c r="F42" s="217" t="n"/>
+      <c r="G42" s="217" t="n"/>
+      <c r="H42" s="222" t="n">
         <v>734.4</v>
       </c>
-      <c r="I42" s="211" t="n">
+      <c r="I42" s="217" t="n">
         <v>783.5</v>
       </c>
-      <c r="J42" s="211" t="n">
+      <c r="J42" s="217" t="n">
         <v>822.7</v>
       </c>
-      <c r="K42" s="211" t="n">
+      <c r="K42" s="217" t="n">
         <v>851.5</v>
       </c>
-      <c r="L42" s="211" t="n">
+      <c r="L42" s="217" t="n">
         <v>872.8</v>
       </c>
-      <c r="M42" s="211" t="n">
+      <c r="M42" s="217" t="n">
         <v>890.2</v>
       </c>
-      <c r="N42" s="211" t="n">
+      <c r="N42" s="217" t="n">
         <v>903.6</v>
       </c>
-      <c r="O42" s="211" t="n"/>
-      <c r="P42" s="211" t="n"/>
+      <c r="O42" s="217" t="n"/>
+      <c r="P42" s="217" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="59" t="inlineStr">
+      <c r="B43" s="57" t="inlineStr">
         <is>
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="C43" s="222" t="n"/>
-      <c r="D43" s="223" t="n"/>
-      <c r="E43" s="223" t="n"/>
-      <c r="F43" s="223" t="n"/>
-      <c r="G43" s="223" t="n"/>
-      <c r="H43" s="222">
+      <c r="C43" s="228" t="n"/>
+      <c r="D43" s="229" t="n"/>
+      <c r="E43" s="229" t="n"/>
+      <c r="F43" s="229" t="n"/>
+      <c r="G43" s="229" t="n"/>
+      <c r="H43" s="228">
         <f>H39+H41-H40-H42</f>
         <v/>
       </c>
-      <c r="I43" s="223">
+      <c r="I43" s="229">
         <f>I39+I41-I40-I42</f>
         <v/>
       </c>
-      <c r="J43" s="223">
+      <c r="J43" s="229">
         <f>J39+J41-J40-J42</f>
         <v/>
       </c>
-      <c r="K43" s="223">
+      <c r="K43" s="229">
         <f>K39+K41-K40-K42</f>
         <v/>
       </c>
-      <c r="L43" s="223">
+      <c r="L43" s="229">
         <f>L39+L41-L40-L42</f>
         <v/>
       </c>
-      <c r="M43" s="223">
+      <c r="M43" s="229">
         <f>M39+M41-M40-M42</f>
         <v/>
       </c>
-      <c r="N43" s="223">
+      <c r="N43" s="229">
         <f>N39+N41-N40-N42</f>
         <v/>
       </c>
-      <c r="O43" s="223" t="n"/>
-      <c r="P43" s="223" t="n"/>
+      <c r="O43" s="229" t="n"/>
+      <c r="P43" s="229" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="14" t="inlineStr">
@@ -3373,47 +4358,47 @@
           <t>Discounted CF</t>
         </is>
       </c>
-      <c r="H46" s="225">
+      <c r="H46" s="231">
         <f>H43*H44</f>
         <v/>
       </c>
-      <c r="I46" s="226">
+      <c r="I46" s="232">
         <f>I43*I44</f>
         <v/>
       </c>
-      <c r="J46" s="226">
+      <c r="J46" s="232">
         <f>J43*J44</f>
         <v/>
       </c>
-      <c r="K46" s="226">
+      <c r="K46" s="232">
         <f>K43*K44</f>
         <v/>
       </c>
-      <c r="L46" s="226">
+      <c r="L46" s="232">
         <f>L43*L44</f>
         <v/>
       </c>
-      <c r="M46" s="226">
+      <c r="M46" s="232">
         <f>M43*M44</f>
         <v/>
       </c>
-      <c r="N46" s="226">
+      <c r="N46" s="232">
         <f>N43*N44</f>
         <v/>
       </c>
-      <c r="O46" s="226" t="n"/>
-      <c r="P46" s="226" t="n"/>
-      <c r="Q46" s="226" t="n"/>
-      <c r="R46" s="226" t="n"/>
-      <c r="S46" s="226" t="n"/>
-      <c r="T46" s="226" t="n"/>
-      <c r="U46" s="226" t="n"/>
-      <c r="V46" s="226" t="n"/>
+      <c r="O46" s="232" t="n"/>
+      <c r="P46" s="232" t="n"/>
+      <c r="Q46" s="232" t="n"/>
+      <c r="R46" s="232" t="n"/>
+      <c r="S46" s="232" t="n"/>
+      <c r="T46" s="232" t="n"/>
+      <c r="U46" s="232" t="n"/>
+      <c r="V46" s="232" t="n"/>
       <c r="W46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="14" t="n"/>
-      <c r="C47" s="226" t="n"/>
+      <c r="C47" s="232" t="n"/>
       <c r="D47" s="14" t="n"/>
       <c r="E47" s="14" t="n"/>
       <c r="F47" s="14" t="n"/>
@@ -3422,7 +4407,7 @@
           <t>Sum of discounted CF</t>
         </is>
       </c>
-      <c r="H47" s="225">
+      <c r="H47" s="231">
         <f>SUM(H46:N46)</f>
         <v/>
       </c>
@@ -3453,7 +4438,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="H48" s="225">
+      <c r="H48" s="231">
         <f>N43*(1+$C$4)/($C$8-$C$4)</f>
         <v/>
       </c>
@@ -3471,7 +4456,7 @@
       <c r="T48" s="14" t="n"/>
       <c r="U48" s="14" t="n"/>
       <c r="V48" s="14" t="n"/>
-      <c r="W48" s="226" t="n"/>
+      <c r="W48" s="232" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="14" t="n"/>
@@ -3484,7 +4469,7 @@
           <t>Discounted TV</t>
         </is>
       </c>
-      <c r="H49" s="225">
+      <c r="H49" s="231">
         <f>H48*N44</f>
         <v/>
       </c>
@@ -3502,7 +4487,7 @@
       <c r="T49" s="14" t="n"/>
       <c r="U49" s="14" t="n"/>
       <c r="V49" s="14" t="n"/>
-      <c r="W49" s="226" t="n"/>
+      <c r="W49" s="232" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="14" t="n"/>
@@ -3510,12 +4495,12 @@
       <c r="D50" s="14" t="n"/>
       <c r="E50" s="14" t="n"/>
       <c r="F50" s="14" t="n"/>
-      <c r="G50" s="61" t="inlineStr">
+      <c r="G50" s="59" t="inlineStr">
         <is>
           <t>Firm Value</t>
         </is>
       </c>
-      <c r="H50" s="227">
+      <c r="H50" s="233">
         <f>H47+H49</f>
         <v/>
       </c>
@@ -3560,264 +4545,264 @@
       <c r="W51" s="14" t="n"/>
     </row>
     <row r="52">
-      <c r="C52" s="228" t="n"/>
-      <c r="D52" s="228" t="n"/>
-      <c r="E52" s="228" t="n"/>
-      <c r="F52" s="228" t="n"/>
-      <c r="G52" s="228" t="n"/>
-      <c r="H52" s="229" t="n"/>
-      <c r="I52" s="229" t="n"/>
-      <c r="J52" s="229" t="n"/>
-      <c r="K52" s="229" t="n"/>
-      <c r="L52" s="229" t="n"/>
-      <c r="M52" s="229" t="n"/>
-      <c r="N52" s="229" t="n"/>
-      <c r="O52" s="229" t="n"/>
-      <c r="P52" s="229" t="n"/>
-      <c r="Q52" s="229" t="n"/>
-      <c r="R52" s="229" t="n"/>
-      <c r="S52" s="229" t="n"/>
-      <c r="T52" s="229" t="n"/>
-      <c r="U52" s="229" t="n"/>
-      <c r="V52" s="229" t="n"/>
-      <c r="W52" s="229" t="n"/>
+      <c r="C52" s="234" t="n"/>
+      <c r="D52" s="234" t="n"/>
+      <c r="E52" s="234" t="n"/>
+      <c r="F52" s="234" t="n"/>
+      <c r="G52" s="234" t="n"/>
+      <c r="H52" s="235" t="n"/>
+      <c r="I52" s="235" t="n"/>
+      <c r="J52" s="235" t="n"/>
+      <c r="K52" s="235" t="n"/>
+      <c r="L52" s="235" t="n"/>
+      <c r="M52" s="235" t="n"/>
+      <c r="N52" s="235" t="n"/>
+      <c r="O52" s="235" t="n"/>
+      <c r="P52" s="235" t="n"/>
+      <c r="Q52" s="235" t="n"/>
+      <c r="R52" s="235" t="n"/>
+      <c r="S52" s="235" t="n"/>
+      <c r="T52" s="235" t="n"/>
+      <c r="U52" s="235" t="n"/>
+      <c r="V52" s="235" t="n"/>
+      <c r="W52" s="235" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="B53" s="230" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Firm value sensitivity analysis</t>
         </is>
       </c>
-      <c r="C53" s="231" t="n"/>
-      <c r="D53" s="230" t="n"/>
-      <c r="E53" s="230" t="n"/>
-      <c r="F53" s="230" t="n"/>
-      <c r="G53" s="230" t="n"/>
-      <c r="I53" s="230" t="inlineStr">
+      <c r="C53" s="50" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>Equity value sensitivity analysis</t>
         </is>
       </c>
-      <c r="J53" s="231" t="n"/>
-      <c r="K53" s="230" t="n"/>
-      <c r="L53" s="230" t="n"/>
-      <c r="M53" s="230" t="n"/>
-      <c r="N53" s="230" t="n"/>
+      <c r="J53" s="50" t="n"/>
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="6" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="B54" s="232" t="inlineStr">
+      <c r="B54" s="51" t="inlineStr">
         <is>
           <t>WACC / LTG</t>
         </is>
       </c>
-      <c r="C54" s="233" t="n"/>
-      <c r="D54" s="233" t="n"/>
-      <c r="E54" s="233" t="n"/>
-      <c r="F54" s="233" t="n"/>
-      <c r="G54" s="233" t="n"/>
-      <c r="I54" s="232" t="inlineStr">
+      <c r="C54" s="236" t="n"/>
+      <c r="D54" s="236" t="n"/>
+      <c r="E54" s="236" t="n"/>
+      <c r="F54" s="236" t="n"/>
+      <c r="G54" s="236" t="n"/>
+      <c r="I54" s="51" t="inlineStr">
         <is>
           <t>WACC / LTG</t>
         </is>
       </c>
-      <c r="J54" s="233" t="n"/>
-      <c r="K54" s="233" t="n"/>
-      <c r="L54" s="233" t="n"/>
-      <c r="M54" s="233" t="n"/>
-      <c r="N54" s="233" t="n"/>
+      <c r="J54" s="236" t="n"/>
+      <c r="K54" s="236" t="n"/>
+      <c r="L54" s="236" t="n"/>
+      <c r="M54" s="236" t="n"/>
+      <c r="N54" s="236" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="233" t="inlineStr">
+      <c r="B55" s="236" t="inlineStr">
         <is>
           <t>WACC \ LTG</t>
         </is>
       </c>
-      <c r="C55" s="234" t="n">
+      <c r="C55" s="155" t="n">
         <v>0.005</v>
       </c>
-      <c r="D55" s="234" t="n">
+      <c r="D55" s="155" t="n">
         <v>0.01</v>
       </c>
-      <c r="E55" s="234" t="n">
+      <c r="E55" s="155" t="n">
         <v>0.015</v>
       </c>
-      <c r="F55" s="234" t="n">
+      <c r="F55" s="155" t="n">
         <v>0.02</v>
       </c>
-      <c r="G55" s="234" t="n">
+      <c r="G55" s="155" t="n">
         <v>0.025</v>
       </c>
-      <c r="I55" s="233" t="inlineStr">
+      <c r="I55" s="236" t="inlineStr">
         <is>
           <t>WACC \ LTG</t>
         </is>
       </c>
-      <c r="J55" s="234" t="n">
+      <c r="J55" s="155" t="n">
         <v>0.005</v>
       </c>
-      <c r="K55" s="234" t="n">
+      <c r="K55" s="155" t="n">
         <v>0.01</v>
       </c>
-      <c r="L55" s="234" t="n">
+      <c r="L55" s="155" t="n">
         <v>0.015</v>
       </c>
-      <c r="M55" s="234" t="n">
+      <c r="M55" s="155" t="n">
         <v>0.02</v>
       </c>
-      <c r="N55" s="234" t="n">
+      <c r="N55" s="155" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="201" t="n"/>
-      <c r="B56" s="233" t="n">
+      <c r="A56" s="195" t="n"/>
+      <c r="B56" s="236" t="n">
         <v>0.06430000000000001</v>
       </c>
-      <c r="C56" s="234" t="n">
+      <c r="C56" s="155" t="n">
         <v>38092</v>
       </c>
-      <c r="D56" s="234" t="n">
+      <c r="D56" s="155" t="n">
         <v>40661</v>
       </c>
-      <c r="E56" s="234" t="n">
+      <c r="E56" s="155" t="n">
         <v>43750</v>
       </c>
-      <c r="F56" s="234" t="n">
+      <c r="F56" s="155" t="n">
         <v>47538</v>
       </c>
-      <c r="G56" s="234" t="n">
+      <c r="G56" s="155" t="n">
         <v>52289</v>
       </c>
-      <c r="I56" s="233" t="n">
+      <c r="I56" s="236" t="n">
         <v>0.06430000000000001</v>
       </c>
-      <c r="J56" s="234" t="n">
+      <c r="J56" s="155" t="n">
         <v>63.92</v>
       </c>
-      <c r="K56" s="234" t="n">
+      <c r="K56" s="155" t="n">
         <v>69.06</v>
       </c>
-      <c r="L56" s="234" t="n">
+      <c r="L56" s="155" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="M56" s="234" t="n">
+      <c r="M56" s="155" t="n">
         <v>82.81</v>
       </c>
-      <c r="N56" s="234" t="n">
+      <c r="N56" s="155" t="n">
         <v>92.31</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="233" t="n">
+      <c r="B57" s="236" t="n">
         <v>0.0693</v>
       </c>
-      <c r="C57" s="234" t="n">
+      <c r="C57" s="155" t="n">
         <v>35207</v>
       </c>
-      <c r="D57" s="234" t="n">
+      <c r="D57" s="155" t="n">
         <v>37326</v>
       </c>
-      <c r="E57" s="234" t="n">
+      <c r="E57" s="155" t="n">
         <v>39835</v>
       </c>
-      <c r="F57" s="234" t="n">
+      <c r="F57" s="155" t="n">
         <v>42854</v>
       </c>
-      <c r="G57" s="235" t="n">
+      <c r="G57" s="11" t="n">
         <v>46553</v>
       </c>
-      <c r="I57" s="233" t="n">
+      <c r="I57" s="236" t="n">
         <v>0.0693</v>
       </c>
-      <c r="J57" s="234" t="n">
+      <c r="J57" s="155" t="n">
         <v>58.15</v>
       </c>
-      <c r="K57" s="234" t="n">
+      <c r="K57" s="155" t="n">
         <v>62.39</v>
       </c>
-      <c r="L57" s="234" t="n">
+      <c r="L57" s="155" t="n">
         <v>67.41</v>
       </c>
-      <c r="M57" s="234" t="n">
+      <c r="M57" s="155" t="n">
         <v>73.44</v>
       </c>
-      <c r="N57" s="235" t="n">
+      <c r="N57" s="11" t="n">
         <v>80.84</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="233" t="n">
+      <c r="B58" s="236" t="n">
         <v>0.0743</v>
       </c>
-      <c r="C58" s="234" t="n">
+      <c r="C58" s="155" t="n">
         <v>32739</v>
       </c>
-      <c r="D58" s="234" t="n">
+      <c r="D58" s="155" t="n">
         <v>34511</v>
       </c>
-      <c r="E58" s="234" t="n">
+      <c r="E58" s="155" t="n">
         <v>36581</v>
       </c>
-      <c r="F58" s="234" t="n">
+      <c r="F58" s="155" t="n">
         <v>39032</v>
       </c>
-      <c r="G58" s="235" t="n">
+      <c r="G58" s="11" t="n">
         <v>41981</v>
       </c>
-      <c r="I58" s="233" t="n">
+      <c r="I58" s="236" t="n">
         <v>0.0743</v>
       </c>
-      <c r="J58" s="234" t="n">
+      <c r="J58" s="155" t="n">
         <v>53.21</v>
       </c>
-      <c r="K58" s="234" t="n">
+      <c r="K58" s="155" t="n">
         <v>56.76</v>
       </c>
-      <c r="L58" s="234" t="n">
+      <c r="L58" s="155" t="n">
         <v>60.9</v>
       </c>
-      <c r="M58" s="234" t="n">
+      <c r="M58" s="155" t="n">
         <v>65.8</v>
       </c>
-      <c r="N58" s="235" t="n">
+      <c r="N58" s="11" t="n">
         <v>71.7</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="233" t="n">
+      <c r="B59" s="236" t="n">
         <v>0.07930000000000001</v>
       </c>
-      <c r="C59" s="234" t="n">
+      <c r="C59" s="155" t="n">
         <v>30604</v>
       </c>
-      <c r="D59" s="234" t="n">
+      <c r="D59" s="155" t="n">
         <v>32102</v>
       </c>
-      <c r="E59" s="234" t="n">
+      <c r="E59" s="155" t="n">
         <v>33832</v>
       </c>
-      <c r="F59" s="234" t="n">
+      <c r="F59" s="155" t="n">
         <v>35855</v>
       </c>
-      <c r="G59" s="235" t="n">
+      <c r="G59" s="11" t="n">
         <v>38250</v>
       </c>
-      <c r="I59" s="233" t="n">
+      <c r="I59" s="236" t="n">
         <v>0.07930000000000001</v>
       </c>
-      <c r="J59" s="234" t="n">
+      <c r="J59" s="155" t="n">
         <v>48.94</v>
       </c>
-      <c r="K59" s="234" t="n">
+      <c r="K59" s="155" t="n">
         <v>51.94</v>
       </c>
-      <c r="L59" s="234" t="n">
+      <c r="L59" s="155" t="n">
         <v>55.4</v>
       </c>
-      <c r="M59" s="234" t="n">
+      <c r="M59" s="155" t="n">
         <v>59.45</v>
       </c>
-      <c r="N59" s="235" t="n">
+      <c r="N59" s="11" t="n">
         <v>64.23999999999999</v>
       </c>
     </row>
@@ -3860,583 +4845,49 @@
       </c>
     </row>
     <row r="64">
-      <c r="C64" s="236" t="n"/>
-      <c r="E64" s="236" t="n"/>
-      <c r="J64" s="229" t="n"/>
-      <c r="K64" s="229" t="n"/>
-      <c r="L64" s="229" t="n"/>
-      <c r="M64" s="229" t="n"/>
-      <c r="N64" s="229" t="n"/>
+      <c r="C64" s="179" t="n"/>
+      <c r="E64" s="179" t="n"/>
+      <c r="J64" s="235" t="n"/>
+      <c r="K64" s="235" t="n"/>
+      <c r="L64" s="235" t="n"/>
+      <c r="M64" s="235" t="n"/>
+      <c r="N64" s="235" t="n"/>
     </row>
     <row r="65">
-      <c r="J65" s="229" t="n"/>
-      <c r="K65" s="229" t="n"/>
-      <c r="L65" s="229" t="n"/>
-      <c r="M65" s="229" t="n"/>
-      <c r="N65" s="229" t="n"/>
+      <c r="J65" s="235" t="n"/>
+      <c r="K65" s="235" t="n"/>
+      <c r="L65" s="235" t="n"/>
+      <c r="M65" s="235" t="n"/>
+      <c r="N65" s="235" t="n"/>
     </row>
     <row r="66">
-      <c r="J66" s="229" t="n"/>
-      <c r="K66" s="229" t="n"/>
-      <c r="L66" s="229" t="n"/>
-      <c r="M66" s="229" t="n"/>
-      <c r="N66" s="229" t="n"/>
+      <c r="J66" s="235" t="n"/>
+      <c r="K66" s="235" t="n"/>
+      <c r="L66" s="235" t="n"/>
+      <c r="M66" s="235" t="n"/>
+      <c r="N66" s="235" t="n"/>
     </row>
     <row r="67">
-      <c r="J67" s="229" t="n"/>
-      <c r="K67" s="229" t="n"/>
-      <c r="L67" s="229" t="n"/>
-      <c r="M67" s="229" t="n"/>
-      <c r="N67" s="229" t="n"/>
+      <c r="J67" s="235" t="n"/>
+      <c r="K67" s="235" t="n"/>
+      <c r="L67" s="235" t="n"/>
+      <c r="M67" s="235" t="n"/>
+      <c r="N67" s="235" t="n"/>
     </row>
     <row r="68">
-      <c r="J68" s="229" t="n"/>
-      <c r="K68" s="229" t="n"/>
-      <c r="L68" s="229" t="n"/>
-      <c r="M68" s="229" t="n"/>
-      <c r="N68" s="229" t="n"/>
+      <c r="J68" s="235" t="n"/>
+      <c r="K68" s="235" t="n"/>
+      <c r="L68" s="235" t="n"/>
+      <c r="M68" s="235" t="n"/>
+      <c r="N68" s="235" t="n"/>
     </row>
     <row r="74">
-      <c r="J74" s="236" t="n"/>
+      <c r="J74" s="179" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A56:A60"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:O35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" style="1" min="1" max="1"/>
-    <col width="40.28515625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="16.28515625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="11" customWidth="1" style="1" min="4" max="8"/>
-    <col width="21.7109375" customWidth="1" style="1" min="9" max="9"/>
-    <col width="11" customWidth="1" style="1" min="10" max="13"/>
-    <col width="12.7109375" customWidth="1" style="1" min="14" max="14"/>
-    <col width="11" customWidth="1" style="1" min="15" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="34" t="inlineStr">
-        <is>
-          <t>Cost of Equity:</t>
-        </is>
-      </c>
-      <c r="C2" s="35" t="n"/>
-      <c r="F2" s="17" t="inlineStr">
-        <is>
-          <t>Peer group (adjusted) Betas</t>
-        </is>
-      </c>
-      <c r="G2" s="17" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="22" t="inlineStr">
-        <is>
-          <t>Net debt</t>
-        </is>
-      </c>
-      <c r="J2" s="17" t="inlineStr">
-        <is>
-          <t>Tax-rate</t>
-        </is>
-      </c>
-      <c r="K2" s="17" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="L2" s="17" t="inlineStr">
-        <is>
-          <t>D/E</t>
-        </is>
-      </c>
-      <c r="M2" s="17" t="inlineStr">
-        <is>
-          <t>Unlevered Beta</t>
-        </is>
-      </c>
-      <c r="N2" s="58" t="n"/>
-      <c r="O2" s="58" t="n"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="12" t="n"/>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>Daimler Truck</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="n"/>
-      <c r="H3" s="23" t="n"/>
-      <c r="I3" s="237" t="n">
-        <v>-7578</v>
-      </c>
-      <c r="J3" s="208" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K3" s="237" t="n">
-        <v>32309</v>
-      </c>
-      <c r="L3" s="208" t="n">
-        <v>-0.2345476492618156</v>
-      </c>
-      <c r="M3" s="238" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="N3" s="79" t="n"/>
-      <c r="O3" s="79" t="n"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="C4" s="210" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>Volvo</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="n"/>
-      <c r="H4" s="23" t="n"/>
-      <c r="I4" s="237" t="n">
-        <v>-43938</v>
-      </c>
-      <c r="J4" s="208" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K4" s="237" t="n">
-        <v>683894</v>
-      </c>
-      <c r="L4" s="208" t="n">
-        <v>-0.06424679848046627</v>
-      </c>
-      <c r="M4" s="238" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="N4" s="79" t="n"/>
-      <c r="O4" s="79" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Equity market premium (Germany):</t>
-        </is>
-      </c>
-      <c r="C5" s="239" t="n">
-        <v>0.0423</v>
-      </c>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="23" t="n"/>
-      <c r="I5" s="237" t="n"/>
-      <c r="J5" s="208" t="n"/>
-      <c r="K5" s="237" t="n"/>
-      <c r="L5" s="208" t="n"/>
-      <c r="M5" s="238" t="n"/>
-      <c r="N5" s="79" t="n"/>
-      <c r="O5" s="79" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Debt / Capital Ratio</t>
-        </is>
-      </c>
-      <c r="C6" s="210" t="n">
-        <v>0.2148232287377538</v>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>Peer average</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="23" t="n"/>
-      <c r="I6" s="237" t="n"/>
-      <c r="J6" s="208" t="n"/>
-      <c r="K6" s="237" t="n"/>
-      <c r="L6" s="208" t="n"/>
-      <c r="M6" s="238" t="n"/>
-      <c r="N6" s="79" t="n"/>
-      <c r="O6" s="79" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Re-levered beta:</t>
-        </is>
-      </c>
-      <c r="C7" s="81" t="n">
-        <v>1.198</v>
-      </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="23" t="n"/>
-      <c r="I7" s="237" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="237" t="n"/>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="79" t="n"/>
-      <c r="N7" s="79" t="n"/>
-      <c r="O7" s="79" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="133" t="n"/>
-      <c r="C8" s="240" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="23" t="n"/>
-      <c r="I8" s="237" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="237" t="n"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="79" t="n"/>
-      <c r="N8" s="79" t="n"/>
-      <c r="O8" s="79" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="23" t="n"/>
-      <c r="I9" s="237" t="n"/>
-      <c r="J9" s="15" t="n"/>
-      <c r="K9" s="237" t="n"/>
-      <c r="L9" s="15" t="n"/>
-      <c r="M9" s="79" t="n"/>
-      <c r="N9" s="79" t="n"/>
-      <c r="O9" s="79" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Cost of Equity (CAPM):</t>
-        </is>
-      </c>
-      <c r="C10" s="241" t="n">
-        <v>0.0857</v>
-      </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="23" t="n"/>
-      <c r="I10" s="237" t="n"/>
-      <c r="J10" s="15" t="n"/>
-      <c r="K10" s="237" t="n"/>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="79" t="n"/>
-      <c r="N10" s="79" t="n"/>
-      <c r="O10" s="79" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="23" t="n"/>
-      <c r="I11" s="237" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="237" t="n"/>
-      <c r="L11" s="15" t="n"/>
-      <c r="M11" s="79" t="n"/>
-      <c r="N11" s="79" t="n"/>
-      <c r="O11" s="79" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cost of Debt: </t>
-        </is>
-      </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="23" t="n"/>
-      <c r="I12" s="237" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="237" t="n"/>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="79" t="n"/>
-      <c r="N12" s="79" t="n"/>
-      <c r="O12" s="79" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>CDS spread (?Y)</t>
-        </is>
-      </c>
-      <c r="C13" s="210" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="23" t="n"/>
-      <c r="I13" s="237" t="n"/>
-      <c r="J13" s="15" t="n"/>
-      <c r="K13" s="237" t="n"/>
-      <c r="L13" s="15" t="n"/>
-      <c r="M13" s="79" t="n"/>
-      <c r="N13" s="79" t="n"/>
-      <c r="O13" s="79" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="C14" s="210" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="23" t="n"/>
-      <c r="I14" s="237" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="237" t="n"/>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="79" t="n"/>
-      <c r="N14" s="79" t="n"/>
-      <c r="O14" s="79" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Pre-tax cost of debt</t>
-        </is>
-      </c>
-      <c r="C15" s="210" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="242" t="n"/>
-      <c r="J15" s="30" t="n"/>
-      <c r="K15" s="243" t="n"/>
-      <c r="L15" s="30" t="n"/>
-      <c r="M15" s="80" t="n"/>
-      <c r="N15" s="79" t="n"/>
-      <c r="O15" s="79" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" thickTop="1">
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="C16" s="210" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="244" t="n"/>
-      <c r="I16" s="244" t="n"/>
-      <c r="J16" s="244" t="n"/>
-      <c r="K16" s="244" t="n"/>
-      <c r="L16" s="244" t="n"/>
-      <c r="M16" s="245" t="n"/>
-      <c r="N16" s="244" t="n"/>
-      <c r="O16" s="244" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>After-tax cost of debt</t>
-        </is>
-      </c>
-      <c r="C17" s="210" t="n">
-        <v>0.0329</v>
-      </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="244" t="n"/>
-      <c r="I17" s="244" t="n"/>
-      <c r="J17" s="244" t="n"/>
-      <c r="K17" s="244" t="n"/>
-      <c r="L17" s="244" t="n"/>
-      <c r="M17" s="245" t="n"/>
-      <c r="N17" s="245" t="n"/>
-      <c r="O17" s="245" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="J18" s="246" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cost of Debt: </t>
-        </is>
-      </c>
-      <c r="C20" s="247" t="n">
-        <v>0.0329</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="K21" s="40" t="n"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>WACC:</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="n"/>
-      <c r="K22" s="14" t="n"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="14" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="33" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="K23" s="14" t="n"/>
-      <c r="L23" s="134" t="n"/>
-      <c r="M23" s="134" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Equity market value</t>
-        </is>
-      </c>
-      <c r="C24" s="25" t="n">
-        <v>16590</v>
-      </c>
-      <c r="K24" s="14" t="n"/>
-      <c r="L24" s="46" t="n"/>
-      <c r="M24" s="46" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>Net debt incl. EV adj.</t>
-        </is>
-      </c>
-      <c r="C25" s="195" t="n">
-        <v>4539</v>
-      </c>
-      <c r="K25" s="14" t="n"/>
-      <c r="L25" s="46" t="n"/>
-      <c r="M25" s="46" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Debt / Capital</t>
-        </is>
-      </c>
-      <c r="C26" s="210" t="n">
-        <v>0.2148232287377538</v>
-      </c>
-      <c r="K26" s="14" t="n"/>
-      <c r="L26" s="46" t="n"/>
-      <c r="M26" s="46" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Equity / Capital</t>
-        </is>
-      </c>
-      <c r="C27" s="210" t="n">
-        <v>0.7851767712622462</v>
-      </c>
-      <c r="K27" s="14" t="n"/>
-      <c r="L27" s="46" t="n"/>
-      <c r="M27" s="46" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Target D/E</t>
-        </is>
-      </c>
-      <c r="C28" s="210" t="n">
-        <v>0.2735985533453888</v>
-      </c>
-      <c r="K28" s="14" t="n"/>
-      <c r="L28" s="46" t="n"/>
-      <c r="M28" s="46" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="C29" s="239" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K29" s="14" t="n"/>
-      <c r="L29" s="46" t="n"/>
-      <c r="M29" s="46" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="46" t="n"/>
-      <c r="M30" s="46" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="22" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C31" s="248" t="n">
-        <v>0.0743</v>
-      </c>
-      <c r="K31" s="14" t="n"/>
-      <c r="L31" s="135" t="n"/>
-      <c r="M31" s="135" t="n"/>
-    </row>
-    <row r="32">
-      <c r="K32" s="14" t="n"/>
-      <c r="L32" s="135" t="n"/>
-      <c r="M32" s="135" t="n"/>
-    </row>
-    <row r="33">
-      <c r="K33" s="14" t="n"/>
-      <c r="L33" s="14" t="n"/>
-      <c r="M33" s="14" t="n"/>
-    </row>
-    <row r="34">
-      <c r="K34" s="14" t="n"/>
-      <c r="L34" s="14" t="n"/>
-      <c r="M34" s="135" t="n"/>
-    </row>
-    <row r="35">
-      <c r="K35" s="14" t="n"/>
-      <c r="L35" s="14" t="n"/>
-      <c r="M35" s="135" t="n"/>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
@@ -4448,191 +4899,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15"/>
+  <dimension ref="B2:O35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11" customWidth="1" style="1" min="1" max="1"/>
-    <col width="27.28515625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="11" customWidth="1" style="1" min="4" max="16384"/>
+    <col width="11" customWidth="1" style="196" min="1" max="1"/>
+    <col width="40.33203125" customWidth="1" style="196" min="2" max="2"/>
+    <col width="16.33203125" customWidth="1" style="196" min="3" max="3"/>
+    <col width="11" customWidth="1" style="196" min="4" max="8"/>
+    <col width="21.6640625" customWidth="1" style="196" min="9" max="9"/>
+    <col width="11" customWidth="1" style="196" min="10" max="13"/>
+    <col width="12.6640625" customWidth="1" style="196" min="14" max="14"/>
+    <col width="11" customWidth="1" style="196" min="15" max="15"/>
+    <col width="11" customWidth="1" style="196" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="249" t="inlineStr">
-        <is>
-          <t>Equity Bridge:</t>
-        </is>
-      </c>
-      <c r="C2" s="250" t="n"/>
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>Cost of Equity:</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="n"/>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>Peer group (adjusted) Betas</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="22" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t>Tax-rate</t>
+        </is>
+      </c>
+      <c r="K2" s="17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="L2" s="17" t="inlineStr">
+        <is>
+          <t>D/E</t>
+        </is>
+      </c>
+      <c r="M2" s="17" t="inlineStr">
+        <is>
+          <t>Unlevered Beta</t>
+        </is>
+      </c>
+      <c r="N2" s="56" t="n"/>
+      <c r="O2" s="56" t="n"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Daimler Truck</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="n"/>
+      <c r="H3" s="23" t="n"/>
+      <c r="I3" s="237" t="n">
+        <v>-7578</v>
+      </c>
+      <c r="J3" s="214" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K3" s="237" t="n">
+        <v>32309</v>
+      </c>
+      <c r="L3" s="214" t="n">
+        <v>-0.2345476492618156</v>
+      </c>
+      <c r="M3" s="238" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="N3" s="76" t="n"/>
+      <c r="O3" s="76" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Risk-free rate</t>
+        </is>
+      </c>
+      <c r="C4" s="216" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Volvo</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="23" t="n"/>
+      <c r="I4" s="237" t="n">
+        <v>-43938</v>
+      </c>
+      <c r="J4" s="214" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K4" s="237" t="n">
+        <v>683894</v>
+      </c>
+      <c r="L4" s="214" t="n">
+        <v>-0.06424679848046627</v>
+      </c>
+      <c r="M4" s="238" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="N4" s="76" t="n"/>
+      <c r="O4" s="76" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="230" t="inlineStr">
-        <is>
-          <t>Firm Value</t>
-        </is>
-      </c>
-      <c r="C5" s="251">
-        <f>'FCFF &amp; DCF'!H50</f>
-        <v/>
-      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Equity market premium (Germany):</t>
+        </is>
+      </c>
+      <c r="C5" s="239" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="23" t="n"/>
+      <c r="I5" s="237" t="n"/>
+      <c r="J5" s="214" t="n"/>
+      <c r="K5" s="237" t="n"/>
+      <c r="L5" s="214" t="n"/>
+      <c r="M5" s="238" t="n"/>
+      <c r="N5" s="76" t="n"/>
+      <c r="O5" s="76" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="252" t="inlineStr">
-        <is>
-          <t>+ Cash (netted in ind. net debt)</t>
-        </is>
-      </c>
-      <c r="C6" s="253" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Debt / Capital Ratio</t>
+        </is>
+      </c>
+      <c r="C6" s="216" t="n">
+        <v>0.2148232287377538</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Peer average</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="237" t="n"/>
+      <c r="J6" s="214" t="n"/>
+      <c r="K6" s="237" t="n"/>
+      <c r="L6" s="214" t="n"/>
+      <c r="M6" s="238" t="n"/>
+      <c r="N6" s="76" t="n"/>
+      <c r="O6" s="76" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="254" t="inlineStr">
-        <is>
-          <t>- Net industrial debt (EV - MCap)</t>
-        </is>
-      </c>
-      <c r="C7" s="255" t="n">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Re-levered beta:</t>
+        </is>
+      </c>
+      <c r="C7" s="78" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="237" t="n"/>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="237" t="n"/>
+      <c r="L7" s="15" t="n"/>
+      <c r="M7" s="76" t="n"/>
+      <c r="N7" s="76" t="n"/>
+      <c r="O7" s="76" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="128" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="237" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="237" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="76" t="n"/>
+      <c r="N8" s="76" t="n"/>
+      <c r="O8" s="76" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="237" t="n"/>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="237" t="n"/>
+      <c r="L9" s="15" t="n"/>
+      <c r="M9" s="76" t="n"/>
+      <c r="N9" s="76" t="n"/>
+      <c r="O9" s="76" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Cost of Equity (CAPM):</t>
+        </is>
+      </c>
+      <c r="C10" s="240" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="237" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="237" t="n"/>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="76" t="n"/>
+      <c r="N10" s="76" t="n"/>
+      <c r="O10" s="76" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="237" t="n"/>
+      <c r="J11" s="15" t="n"/>
+      <c r="K11" s="237" t="n"/>
+      <c r="L11" s="15" t="n"/>
+      <c r="M11" s="76" t="n"/>
+      <c r="N11" s="76" t="n"/>
+      <c r="O11" s="76" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cost of Debt: </t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="237" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="237" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="76" t="n"/>
+      <c r="N12" s="76" t="n"/>
+      <c r="O12" s="76" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>CDS spread (?Y)</t>
+        </is>
+      </c>
+      <c r="C13" s="216" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="237" t="n"/>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="237" t="n"/>
+      <c r="L13" s="15" t="n"/>
+      <c r="M13" s="76" t="n"/>
+      <c r="N13" s="76" t="n"/>
+      <c r="O13" s="76" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Risk-free rate</t>
+        </is>
+      </c>
+      <c r="C14" s="216" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="23" t="n"/>
+      <c r="I14" s="237" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="237" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="76" t="n"/>
+      <c r="N14" s="76" t="n"/>
+      <c r="O14" s="76" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="C15" s="216" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="241" t="n"/>
+      <c r="J15" s="30" t="n"/>
+      <c r="K15" s="242" t="n"/>
+      <c r="L15" s="30" t="n"/>
+      <c r="M15" s="77" t="n"/>
+      <c r="N15" s="76" t="n"/>
+      <c r="O15" s="76" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" thickTop="1">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="C16" s="216" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="31" t="n"/>
+      <c r="I16" s="31" t="n"/>
+      <c r="J16" s="31" t="n"/>
+      <c r="K16" s="31" t="n"/>
+      <c r="L16" s="31" t="n"/>
+      <c r="M16" s="32" t="n"/>
+      <c r="N16" s="31" t="n"/>
+      <c r="O16" s="31" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>After-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="C17" s="216" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="31" t="n"/>
+      <c r="I17" s="31" t="n"/>
+      <c r="J17" s="31" t="n"/>
+      <c r="K17" s="31" t="n"/>
+      <c r="L17" s="31" t="n"/>
+      <c r="M17" s="32" t="n"/>
+      <c r="N17" s="32" t="n"/>
+      <c r="O17" s="32" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="J18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cost of Debt: </t>
+        </is>
+      </c>
+      <c r="C20" s="243" t="n">
+        <v>0.0329</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="K21" s="40" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>WACC:</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="33" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="129" t="n"/>
+      <c r="M23" s="129" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Equity market value</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>16590</v>
+      </c>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="45" t="n"/>
+      <c r="M24" s="45" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Net debt incl. EV adj.</t>
+        </is>
+      </c>
+      <c r="C25" s="189" t="n">
         <v>4539</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="254" t="inlineStr">
-        <is>
-          <t>- Pensions</t>
-        </is>
-      </c>
-      <c r="C8" s="255" t="n">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="254" t="inlineStr">
-        <is>
-          <t>- Minority Interest</t>
-        </is>
-      </c>
-      <c r="C9" s="255" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="254" t="inlineStr">
-        <is>
-          <t>- Preferred Stock</t>
-        </is>
-      </c>
-      <c r="C10" s="255" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="256" t="inlineStr">
-        <is>
-          <t>Equity Value</t>
-        </is>
-      </c>
-      <c r="C11" s="257">
-        <f>C5+C6-C7-C8-C9-C10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="200" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="254" t="inlineStr">
-        <is>
-          <t>Number of outstanding shares (in m)</t>
-        </is>
-      </c>
-      <c r="C13" s="255" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="254" t="inlineStr">
-        <is>
-          <t>Implied share price</t>
-        </is>
-      </c>
-      <c r="C14" s="258">
-        <f>C11/C13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="254" t="n"/>
-      <c r="C15" s="255" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="254" t="inlineStr">
-        <is>
-          <t>Current share price (30.06.2026)</t>
-        </is>
-      </c>
-      <c r="C16" s="235" t="n">
-        <v>33.18</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="254" t="inlineStr">
-        <is>
-          <t>Implied upside</t>
-        </is>
-      </c>
-      <c r="C17" s="235">
-        <f>C14/C16-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Note: Gross debt is EUR 28,799m but ~22bn is captive Financial-Services debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>(matched by financing receivables) -&gt; use industrial net debt (EV-MCap = 4,539). See A.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="45" t="n"/>
+      <c r="M25" s="45" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Debt / Capital</t>
+        </is>
+      </c>
+      <c r="C26" s="216" t="n">
+        <v>0.2148232287377538</v>
+      </c>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="45" t="n"/>
+      <c r="M26" s="45" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Equity / Capital</t>
+        </is>
+      </c>
+      <c r="C27" s="216" t="n">
+        <v>0.7851767712622462</v>
+      </c>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="45" t="n"/>
+      <c r="M27" s="45" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Target D/E</t>
+        </is>
+      </c>
+      <c r="C28" s="216" t="n">
+        <v>0.2735985533453888</v>
+      </c>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="45" t="n"/>
+      <c r="M28" s="45" t="n"/>
+    </row>
     <row r="29">
-      <c r="B29" s="230" t="n"/>
-      <c r="C29" s="251" t="n"/>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="C29" s="239" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="45" t="n"/>
+      <c r="M29" s="45" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="254" t="n"/>
-      <c r="C30" s="255" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="45" t="n"/>
+      <c r="M30" s="45" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="254" t="n"/>
-      <c r="C31" s="255" t="n"/>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C31" s="244" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="130" t="n"/>
+      <c r="M31" s="130" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="254" t="n"/>
-      <c r="C32" s="255" t="n"/>
+      <c r="K32" s="14" t="n"/>
+      <c r="L32" s="130" t="n"/>
+      <c r="M32" s="130" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="254" t="n"/>
-      <c r="C33" s="255" t="n"/>
+      <c r="K33" s="14" t="n"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="254" t="n"/>
-      <c r="C34" s="255" t="n"/>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="130" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="230" t="n"/>
-      <c r="C35" s="251" t="n"/>
+      <c r="K35" s="14" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="130" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -4642,377 +5434,570 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AA32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15"/>
+  <dimension ref="B2:C35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="11" customWidth="1" style="1" min="3" max="16384"/>
+    <col width="11" customWidth="1" style="196" min="1" max="1"/>
+    <col width="27.33203125" customWidth="1" style="196" min="2" max="2"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="196" min="3" max="3"/>
+    <col width="11" customWidth="1" style="196" min="4" max="4"/>
+    <col width="11" customWidth="1" style="196" min="5" max="16384"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="65" t="n"/>
-      <c r="C2" s="66" t="n"/>
-      <c r="D2" s="205" t="n"/>
-      <c r="P2" s="67" t="n"/>
-      <c r="Q2" s="67" t="n"/>
-      <c r="R2" s="67" t="n"/>
-      <c r="S2" s="67" t="n"/>
-      <c r="T2" s="66" t="n"/>
-      <c r="U2" s="66" t="n"/>
-      <c r="V2" s="66" t="n"/>
-      <c r="W2" s="66" t="n"/>
-      <c r="X2" s="66" t="n"/>
-      <c r="Y2" s="66" t="n"/>
-      <c r="Z2" s="66" t="n"/>
-      <c r="AA2" s="66" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Equity Bridge:</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Firm Value</t>
+        </is>
+      </c>
+      <c r="C5" s="7">
+        <f>'FCFF &amp; DCF'!H50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>+ Cash (netted in ind. net debt)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>- Net industrial debt (EV - MCap)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>- Pensions</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>- Minority Interest</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>- Preferred Stock</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="61" t="inlineStr">
+        <is>
+          <t>Equity Value</t>
+        </is>
+      </c>
+      <c r="C11" s="134">
+        <f>C5+C6-C7-C8-C9-C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="194" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Number of outstanding shares (in m)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Implied share price</t>
+        </is>
+      </c>
+      <c r="C14" s="10">
+        <f>C11/C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Current share price (30.06.2026)</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>33.18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Implied upside</t>
+        </is>
+      </c>
+      <c r="C17" s="11">
+        <f>C14/C16-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Note: Gross debt is EUR 28,799m but ~22bn is captive Financial-Services debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(matched by financing receivables) -&gt; use industrial net debt (EV-MCap = 4,539). See A.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:AA32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="11" customWidth="1" style="196" min="1" max="1"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
+    <col width="11" customWidth="1" style="196" min="3" max="3"/>
+    <col width="11" customWidth="1" style="196" min="4" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="63" t="n"/>
+      <c r="C2" s="64" t="n"/>
+      <c r="D2" s="197" t="n"/>
+      <c r="P2" s="65" t="n"/>
+      <c r="Q2" s="65" t="n"/>
+      <c r="R2" s="65" t="n"/>
+      <c r="S2" s="65" t="n"/>
+      <c r="T2" s="64" t="n"/>
+      <c r="U2" s="64" t="n"/>
+      <c r="V2" s="64" t="n"/>
+      <c r="W2" s="64" t="n"/>
+      <c r="X2" s="64" t="n"/>
+      <c r="Y2" s="64" t="n"/>
+      <c r="Z2" s="64" t="n"/>
+      <c r="AA2" s="64" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="68" t="n"/>
-      <c r="C3" s="205" t="n"/>
-      <c r="D3" s="205" t="n"/>
-      <c r="H3" s="205" t="n"/>
-      <c r="L3" s="205" t="n"/>
-      <c r="P3" s="67" t="n"/>
-      <c r="Q3" s="67" t="n"/>
-      <c r="R3" s="67" t="n"/>
-      <c r="S3" s="67" t="n"/>
-      <c r="T3" s="67" t="n"/>
-      <c r="U3" s="67" t="n"/>
-      <c r="V3" s="67" t="n"/>
-      <c r="W3" s="67" t="n"/>
-      <c r="X3" s="67" t="n"/>
-      <c r="Y3" s="67" t="n"/>
-      <c r="Z3" s="67" t="n"/>
-      <c r="AA3" s="67" t="n"/>
+      <c r="B3" s="66" t="n"/>
+      <c r="C3" s="197" t="n"/>
+      <c r="D3" s="197" t="n"/>
+      <c r="H3" s="197" t="n"/>
+      <c r="L3" s="197" t="n"/>
+      <c r="P3" s="65" t="n"/>
+      <c r="Q3" s="65" t="n"/>
+      <c r="R3" s="65" t="n"/>
+      <c r="S3" s="65" t="n"/>
+      <c r="T3" s="65" t="n"/>
+      <c r="U3" s="65" t="n"/>
+      <c r="V3" s="65" t="n"/>
+      <c r="W3" s="65" t="n"/>
+      <c r="X3" s="65" t="n"/>
+      <c r="Y3" s="65" t="n"/>
+      <c r="Z3" s="65" t="n"/>
+      <c r="AA3" s="65" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="68" t="n"/>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="71" t="n"/>
-      <c r="E4" s="71" t="n"/>
-      <c r="F4" s="71" t="n"/>
-      <c r="G4" s="71" t="n"/>
-      <c r="H4" s="71" t="n"/>
-      <c r="I4" s="71" t="n"/>
-      <c r="J4" s="71" t="n"/>
-      <c r="K4" s="71" t="n"/>
-      <c r="L4" s="72" t="n"/>
-      <c r="M4" s="72" t="n"/>
-      <c r="N4" s="72" t="n"/>
-      <c r="O4" s="72" t="n"/>
-      <c r="P4" s="71" t="n"/>
-      <c r="Q4" s="71" t="n"/>
-      <c r="R4" s="71" t="n"/>
-      <c r="S4" s="71" t="n"/>
-      <c r="T4" s="66" t="n"/>
-      <c r="U4" s="66" t="n"/>
-      <c r="V4" s="66" t="n"/>
-      <c r="W4" s="66" t="n"/>
-      <c r="X4" s="66" t="n"/>
-      <c r="Y4" s="66" t="n"/>
-      <c r="Z4" s="66" t="n"/>
-      <c r="AA4" s="66" t="n"/>
+      <c r="B4" s="66" t="n"/>
+      <c r="C4" s="68" t="n"/>
+      <c r="D4" s="69" t="n"/>
+      <c r="E4" s="69" t="n"/>
+      <c r="F4" s="69" t="n"/>
+      <c r="G4" s="69" t="n"/>
+      <c r="H4" s="69" t="n"/>
+      <c r="I4" s="69" t="n"/>
+      <c r="J4" s="69" t="n"/>
+      <c r="K4" s="69" t="n"/>
+      <c r="L4" s="70" t="n"/>
+      <c r="M4" s="70" t="n"/>
+      <c r="N4" s="70" t="n"/>
+      <c r="O4" s="70" t="n"/>
+      <c r="P4" s="69" t="n"/>
+      <c r="Q4" s="69" t="n"/>
+      <c r="R4" s="69" t="n"/>
+      <c r="S4" s="69" t="n"/>
+      <c r="T4" s="64" t="n"/>
+      <c r="U4" s="64" t="n"/>
+      <c r="V4" s="64" t="n"/>
+      <c r="W4" s="64" t="n"/>
+      <c r="X4" s="64" t="n"/>
+      <c r="Y4" s="64" t="n"/>
+      <c r="Z4" s="64" t="n"/>
+      <c r="AA4" s="64" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="68" t="n"/>
-      <c r="C5" s="70" t="n"/>
-      <c r="D5" s="70" t="n"/>
-      <c r="E5" s="70" t="n"/>
-      <c r="F5" s="70" t="n"/>
-      <c r="G5" s="70" t="n"/>
-      <c r="H5" s="70" t="n"/>
-      <c r="I5" s="70" t="n"/>
-      <c r="J5" s="70" t="n"/>
-      <c r="K5" s="70" t="n"/>
-      <c r="L5" s="70" t="n"/>
-      <c r="M5" s="70" t="n"/>
-      <c r="N5" s="70" t="n"/>
-      <c r="O5" s="70" t="n"/>
-      <c r="P5" s="70" t="n"/>
-      <c r="Q5" s="70" t="n"/>
-      <c r="R5" s="70" t="n"/>
-      <c r="S5" s="70" t="n"/>
-      <c r="T5" s="70" t="n"/>
-      <c r="U5" s="70" t="n"/>
-      <c r="V5" s="70" t="n"/>
-      <c r="W5" s="70" t="n"/>
-      <c r="X5" s="70" t="n"/>
-      <c r="Y5" s="70" t="n"/>
-      <c r="Z5" s="70" t="n"/>
-      <c r="AA5" s="70" t="n"/>
+      <c r="B5" s="66" t="n"/>
+      <c r="C5" s="68" t="n"/>
+      <c r="D5" s="68" t="n"/>
+      <c r="E5" s="68" t="n"/>
+      <c r="F5" s="68" t="n"/>
+      <c r="G5" s="68" t="n"/>
+      <c r="H5" s="68" t="n"/>
+      <c r="I5" s="68" t="n"/>
+      <c r="J5" s="68" t="n"/>
+      <c r="K5" s="68" t="n"/>
+      <c r="L5" s="68" t="n"/>
+      <c r="M5" s="68" t="n"/>
+      <c r="N5" s="68" t="n"/>
+      <c r="O5" s="68" t="n"/>
+      <c r="P5" s="68" t="n"/>
+      <c r="Q5" s="68" t="n"/>
+      <c r="R5" s="68" t="n"/>
+      <c r="S5" s="68" t="n"/>
+      <c r="T5" s="68" t="n"/>
+      <c r="U5" s="68" t="n"/>
+      <c r="V5" s="68" t="n"/>
+      <c r="W5" s="68" t="n"/>
+      <c r="X5" s="68" t="n"/>
+      <c r="Y5" s="68" t="n"/>
+      <c r="Z5" s="68" t="n"/>
+      <c r="AA5" s="68" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="109" t="n"/>
-      <c r="C6" s="110" t="n"/>
-      <c r="D6" s="206" t="inlineStr">
+      <c r="B6" s="106" t="n"/>
+      <c r="C6" s="107" t="n"/>
+      <c r="D6" s="201" t="inlineStr">
         <is>
           <t>Financial Data</t>
         </is>
       </c>
-      <c r="E6" s="259" t="n"/>
-      <c r="F6" s="259" t="n"/>
-      <c r="G6" s="259" t="n"/>
-      <c r="H6" s="259" t="n"/>
-      <c r="I6" s="259" t="n"/>
-      <c r="J6" s="259" t="n"/>
-      <c r="K6" s="259" t="n"/>
-      <c r="L6" s="259" t="n"/>
-      <c r="M6" s="259" t="n"/>
-      <c r="N6" s="259" t="n"/>
-      <c r="O6" s="259" t="n"/>
-      <c r="P6" s="117" t="inlineStr">
+      <c r="E6" s="202" t="n"/>
+      <c r="F6" s="202" t="n"/>
+      <c r="G6" s="202" t="n"/>
+      <c r="H6" s="202" t="n"/>
+      <c r="I6" s="202" t="n"/>
+      <c r="J6" s="202" t="n"/>
+      <c r="K6" s="202" t="n"/>
+      <c r="L6" s="202" t="n"/>
+      <c r="M6" s="202" t="n"/>
+      <c r="N6" s="202" t="n"/>
+      <c r="O6" s="202" t="n"/>
+      <c r="P6" s="114" t="inlineStr">
         <is>
           <t>Valuation</t>
         </is>
       </c>
-      <c r="Q6" s="111" t="n"/>
-      <c r="R6" s="112" t="n"/>
-      <c r="S6" s="112" t="n"/>
-      <c r="T6" s="113" t="n"/>
-      <c r="U6" s="113" t="n"/>
-      <c r="V6" s="113" t="n"/>
-      <c r="W6" s="113" t="n"/>
-      <c r="X6" s="113" t="n"/>
-      <c r="Y6" s="113" t="n"/>
-      <c r="Z6" s="113" t="n"/>
-      <c r="AA6" s="114" t="n"/>
+      <c r="Q6" s="108" t="n"/>
+      <c r="R6" s="109" t="n"/>
+      <c r="S6" s="109" t="n"/>
+      <c r="T6" s="110" t="n"/>
+      <c r="U6" s="110" t="n"/>
+      <c r="V6" s="110" t="n"/>
+      <c r="W6" s="110" t="n"/>
+      <c r="X6" s="110" t="n"/>
+      <c r="Y6" s="110" t="n"/>
+      <c r="Z6" s="110" t="n"/>
+      <c r="AA6" s="111" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="115" t="n"/>
-      <c r="C7" s="116" t="inlineStr">
+      <c r="B7" s="112" t="n"/>
+      <c r="C7" s="113" t="inlineStr">
         <is>
           <t>EV</t>
         </is>
       </c>
-      <c r="D7" s="260" t="inlineStr">
+      <c r="D7" s="198" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="E7" s="261" t="n"/>
-      <c r="F7" s="261" t="n"/>
-      <c r="G7" s="262" t="n"/>
-      <c r="H7" s="260" t="inlineStr">
+      <c r="E7" s="199" t="n"/>
+      <c r="F7" s="199" t="n"/>
+      <c r="G7" s="200" t="n"/>
+      <c r="H7" s="198" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="I7" s="261" t="n"/>
-      <c r="J7" s="261" t="n"/>
-      <c r="K7" s="262" t="n"/>
-      <c r="L7" s="260" t="inlineStr">
+      <c r="I7" s="199" t="n"/>
+      <c r="J7" s="199" t="n"/>
+      <c r="K7" s="200" t="n"/>
+      <c r="L7" s="198" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="M7" s="261" t="n"/>
-      <c r="N7" s="261" t="n"/>
-      <c r="O7" s="262" t="n"/>
-      <c r="P7" s="117" t="inlineStr">
+      <c r="M7" s="199" t="n"/>
+      <c r="N7" s="199" t="n"/>
+      <c r="O7" s="200" t="n"/>
+      <c r="P7" s="114" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="Q7" s="112" t="n"/>
-      <c r="R7" s="118" t="n"/>
-      <c r="S7" s="119" t="n"/>
-      <c r="T7" s="120" t="inlineStr">
+      <c r="Q7" s="109" t="n"/>
+      <c r="R7" s="115" t="n"/>
+      <c r="S7" s="116" t="n"/>
+      <c r="T7" s="117" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
-      <c r="U7" s="118" t="n"/>
-      <c r="V7" s="118" t="n"/>
-      <c r="W7" s="119" t="n"/>
-      <c r="X7" s="120" t="inlineStr">
+      <c r="U7" s="115" t="n"/>
+      <c r="V7" s="115" t="n"/>
+      <c r="W7" s="116" t="n"/>
+      <c r="X7" s="117" t="inlineStr">
         <is>
           <t>EV/EBIT</t>
         </is>
       </c>
-      <c r="Y7" s="118" t="n"/>
-      <c r="Z7" s="118" t="n"/>
-      <c r="AA7" s="119" t="n"/>
+      <c r="Y7" s="115" t="n"/>
+      <c r="Z7" s="115" t="n"/>
+      <c r="AA7" s="116" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="115" t="inlineStr">
+      <c r="B8" s="112" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="C8" s="82" t="n"/>
-      <c r="D8" s="83" t="inlineStr">
+      <c r="C8" s="79" t="n"/>
+      <c r="D8" s="80" t="inlineStr">
         <is>
           <t>(€M)</t>
         </is>
       </c>
-      <c r="E8" s="84" t="n"/>
-      <c r="F8" s="84" t="n"/>
-      <c r="G8" s="85" t="n"/>
-      <c r="H8" s="83" t="inlineStr">
+      <c r="E8" s="81" t="n"/>
+      <c r="F8" s="81" t="n"/>
+      <c r="G8" s="82" t="n"/>
+      <c r="H8" s="80" t="inlineStr">
         <is>
           <t>(€M)</t>
         </is>
       </c>
-      <c r="I8" s="86" t="n"/>
-      <c r="J8" s="86" t="n"/>
-      <c r="K8" s="87" t="n"/>
-      <c r="L8" s="83" t="inlineStr">
+      <c r="I8" s="83" t="n"/>
+      <c r="J8" s="83" t="n"/>
+      <c r="K8" s="84" t="n"/>
+      <c r="L8" s="80" t="inlineStr">
         <is>
           <t>(€M)</t>
         </is>
       </c>
-      <c r="M8" s="88" t="n"/>
-      <c r="N8" s="88" t="n"/>
-      <c r="O8" s="89" t="n"/>
-      <c r="P8" s="90" t="inlineStr">
+      <c r="M8" s="85" t="n"/>
+      <c r="N8" s="85" t="n"/>
+      <c r="O8" s="86" t="n"/>
+      <c r="P8" s="87" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Q8" s="91" t="n"/>
-      <c r="R8" s="91" t="n"/>
-      <c r="S8" s="92" t="n"/>
-      <c r="T8" s="121" t="inlineStr">
+      <c r="Q8" s="88" t="n"/>
+      <c r="R8" s="88" t="n"/>
+      <c r="S8" s="89" t="n"/>
+      <c r="T8" s="118" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="U8" s="122" t="n"/>
-      <c r="V8" s="122" t="n"/>
-      <c r="W8" s="123" t="n"/>
-      <c r="X8" s="121" t="inlineStr">
+      <c r="U8" s="119" t="n"/>
+      <c r="V8" s="119" t="n"/>
+      <c r="W8" s="120" t="n"/>
+      <c r="X8" s="118" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y8" s="122" t="n"/>
-      <c r="Z8" s="122" t="n"/>
-      <c r="AA8" s="123" t="n"/>
+      <c r="Y8" s="119" t="n"/>
+      <c r="Z8" s="119" t="n"/>
+      <c r="AA8" s="120" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="93" t="inlineStr">
+      <c r="B9" s="121" t="n"/>
+      <c r="C9" s="90" t="inlineStr">
         <is>
           <t>(€M)</t>
         </is>
       </c>
-      <c r="D9" s="94" t="inlineStr">
+      <c r="D9" s="91" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="E9" s="95" t="inlineStr">
+      <c r="E9" s="92" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="F9" s="95" t="inlineStr">
+      <c r="F9" s="92" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="G9" s="96" t="inlineStr">
+      <c r="G9" s="93" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="H9" s="94" t="inlineStr">
+      <c r="H9" s="91" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="I9" s="95" t="inlineStr">
+      <c r="I9" s="92" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="J9" s="95" t="inlineStr">
+      <c r="J9" s="92" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="K9" s="96" t="inlineStr">
+      <c r="K9" s="93" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="L9" s="94" t="inlineStr">
+      <c r="L9" s="91" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="M9" s="95" t="inlineStr">
+      <c r="M9" s="92" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="N9" s="95" t="inlineStr">
+      <c r="N9" s="92" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="O9" s="96" t="inlineStr">
+      <c r="O9" s="93" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="P9" s="97" t="inlineStr">
+      <c r="P9" s="94" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="Q9" s="97" t="inlineStr">
+      <c r="Q9" s="94" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="R9" s="97" t="inlineStr">
+      <c r="R9" s="94" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="S9" s="98" t="inlineStr">
+      <c r="S9" s="95" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="T9" s="99" t="inlineStr">
+      <c r="T9" s="96" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="U9" s="97" t="inlineStr">
+      <c r="U9" s="94" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="V9" s="97" t="inlineStr">
+      <c r="V9" s="94" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="W9" s="98" t="inlineStr">
+      <c r="W9" s="95" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="X9" s="99" t="inlineStr">
+      <c r="X9" s="96" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="Y9" s="97" t="inlineStr">
+      <c r="Y9" s="94" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="Z9" s="97" t="inlineStr">
+      <c r="Z9" s="94" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="AA9" s="98" t="inlineStr">
+      <c r="AA9" s="95" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
@@ -5024,90 +6009,90 @@
           <t>Daimler Truck</t>
         </is>
       </c>
-      <c r="C10" s="170" t="n">
+      <c r="C10" s="164" t="n">
         <v>24731</v>
       </c>
-      <c r="D10" s="164" t="n">
+      <c r="D10" s="158" t="n">
         <v>4403</v>
       </c>
-      <c r="E10" s="164" t="n">
+      <c r="E10" s="158" t="n">
         <v>4049</v>
       </c>
-      <c r="F10" s="164" t="n">
+      <c r="F10" s="158" t="n">
         <v>4643</v>
       </c>
-      <c r="G10" s="165" t="n">
+      <c r="G10" s="159" t="n">
         <v>5850</v>
       </c>
-      <c r="H10" s="164" t="n">
+      <c r="H10" s="158" t="n">
         <v>45530</v>
       </c>
-      <c r="I10" s="164" t="n">
+      <c r="I10" s="158" t="n">
         <v>44003</v>
       </c>
-      <c r="J10" s="164" t="n">
+      <c r="J10" s="158" t="n">
         <v>48727</v>
       </c>
-      <c r="K10" s="165" t="n">
+      <c r="K10" s="159" t="n">
         <v>52634</v>
       </c>
-      <c r="L10" s="164" t="n">
+      <c r="L10" s="158" t="n">
         <v>3328</v>
       </c>
-      <c r="M10" s="164" t="n">
+      <c r="M10" s="158" t="n">
         <v>3015</v>
       </c>
-      <c r="N10" s="164" t="n">
+      <c r="N10" s="158" t="n">
         <v>3551</v>
       </c>
-      <c r="O10" s="164" t="n">
+      <c r="O10" s="158" t="n">
         <v>4695</v>
       </c>
-      <c r="P10" s="263">
+      <c r="P10" s="245">
         <f>$C$10/D10</f>
         <v/>
       </c>
-      <c r="Q10" s="264">
+      <c r="Q10" s="246">
         <f>$C$10/E10</f>
         <v/>
       </c>
-      <c r="R10" s="264">
+      <c r="R10" s="246">
         <f>$C$10/F10</f>
         <v/>
       </c>
-      <c r="S10" s="265">
+      <c r="S10" s="247">
         <f>$C$10/G10</f>
         <v/>
       </c>
-      <c r="T10" s="264">
+      <c r="T10" s="246">
         <f>$C$10/H10</f>
         <v/>
       </c>
-      <c r="U10" s="264">
+      <c r="U10" s="246">
         <f>$C$10/I10</f>
         <v/>
       </c>
-      <c r="V10" s="264">
+      <c r="V10" s="246">
         <f>$C$10/J10</f>
         <v/>
       </c>
-      <c r="W10" s="265">
+      <c r="W10" s="247">
         <f>$C$10/K10</f>
         <v/>
       </c>
-      <c r="X10" s="264">
+      <c r="X10" s="246">
         <f>$C$10/L10</f>
         <v/>
       </c>
-      <c r="Y10" s="264">
+      <c r="Y10" s="246">
         <f>$C$10/M10</f>
         <v/>
       </c>
-      <c r="Z10" s="264">
+      <c r="Z10" s="246">
         <f>$C$10/N10</f>
         <v/>
       </c>
-      <c r="AA10" s="265">
+      <c r="AA10" s="247">
         <f>$C$10/O10</f>
         <v/>
       </c>
@@ -5118,1038 +6103,1038 @@
           <t>Volvo</t>
         </is>
       </c>
-      <c r="C11" s="171" t="n">
+      <c r="C11" s="165" t="n">
         <v>639956</v>
       </c>
-      <c r="D11" s="166" t="n">
+      <c r="D11" s="160" t="n">
         <v>75872</v>
       </c>
-      <c r="E11" s="166" t="n">
+      <c r="E11" s="160" t="n">
         <v>69470</v>
       </c>
-      <c r="F11" s="166" t="n">
+      <c r="F11" s="160" t="n">
         <v>78548</v>
       </c>
-      <c r="G11" s="167" t="n">
+      <c r="G11" s="161" t="n">
         <v>88038</v>
       </c>
-      <c r="H11" s="166" t="n">
+      <c r="H11" s="160" t="n">
         <v>479183</v>
       </c>
-      <c r="I11" s="166" t="n">
+      <c r="I11" s="160" t="n">
         <v>468156</v>
       </c>
-      <c r="J11" s="166" t="n">
+      <c r="J11" s="160" t="n">
         <v>491731</v>
       </c>
-      <c r="K11" s="167" t="n">
+      <c r="K11" s="161" t="n">
         <v>528276</v>
       </c>
-      <c r="L11" s="166" t="n">
+      <c r="L11" s="160" t="n">
         <v>53846</v>
       </c>
-      <c r="M11" s="166" t="n">
+      <c r="M11" s="160" t="n">
         <v>45858</v>
       </c>
-      <c r="N11" s="166" t="n">
+      <c r="N11" s="160" t="n">
         <v>56412</v>
       </c>
-      <c r="O11" s="167" t="n">
+      <c r="O11" s="161" t="n">
         <v>66785</v>
       </c>
-      <c r="P11" s="266">
+      <c r="P11" s="248">
         <f>$C$11/D11</f>
         <v/>
       </c>
-      <c r="Q11" s="266">
+      <c r="Q11" s="248">
         <f>$C$11/E11</f>
         <v/>
       </c>
-      <c r="R11" s="266">
+      <c r="R11" s="248">
         <f>$C$11/F11</f>
         <v/>
       </c>
-      <c r="S11" s="267">
+      <c r="S11" s="249">
         <f>$C$11/G11</f>
         <v/>
       </c>
-      <c r="T11" s="266">
+      <c r="T11" s="248">
         <f>$C$11/H11</f>
         <v/>
       </c>
-      <c r="U11" s="266">
+      <c r="U11" s="248">
         <f>$C$11/I11</f>
         <v/>
       </c>
-      <c r="V11" s="266">
+      <c r="V11" s="248">
         <f>$C$11/J11</f>
         <v/>
       </c>
-      <c r="W11" s="267">
+      <c r="W11" s="249">
         <f>$C$11/K11</f>
         <v/>
       </c>
-      <c r="X11" s="266">
+      <c r="X11" s="248">
         <f>$C$11/L11</f>
         <v/>
       </c>
-      <c r="Y11" s="266">
+      <c r="Y11" s="248">
         <f>$C$11/M11</f>
         <v/>
       </c>
-      <c r="Z11" s="266">
+      <c r="Z11" s="248">
         <f>$C$11/N11</f>
         <v/>
       </c>
-      <c r="AA11" s="267">
+      <c r="AA11" s="249">
         <f>$C$11/O11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="64" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>Traton (ref)</t>
         </is>
       </c>
-      <c r="C12" s="180" t="n">
+      <c r="C12" s="174" t="n">
         <v>21129</v>
       </c>
-      <c r="D12" s="168" t="n">
+      <c r="D12" s="162" t="n">
         <v>5966</v>
       </c>
-      <c r="E12" s="168" t="n">
+      <c r="E12" s="162" t="n">
         <v>6072</v>
       </c>
-      <c r="F12" s="168" t="n">
+      <c r="F12" s="162" t="n">
         <v>5719</v>
       </c>
-      <c r="G12" s="169" t="n">
+      <c r="G12" s="163" t="n">
         <v>6723</v>
       </c>
-      <c r="H12" s="168" t="n">
+      <c r="H12" s="162" t="n">
         <v>44051</v>
       </c>
-      <c r="I12" s="168" t="n">
+      <c r="I12" s="162" t="n">
         <v>43675</v>
       </c>
-      <c r="J12" s="168" t="n">
+      <c r="J12" s="162" t="n">
         <v>45897</v>
       </c>
-      <c r="K12" s="169" t="n">
+      <c r="K12" s="163" t="n">
         <v>48970</v>
       </c>
-      <c r="L12" s="168" t="n">
+      <c r="L12" s="162" t="n">
         <v>2819</v>
       </c>
-      <c r="M12" s="168" t="n">
+      <c r="M12" s="162" t="n">
         <v>2731</v>
       </c>
-      <c r="N12" s="168" t="n">
+      <c r="N12" s="162" t="n">
         <v>3049</v>
       </c>
-      <c r="O12" s="169" t="n">
+      <c r="O12" s="163" t="n">
         <v>3986</v>
       </c>
-      <c r="P12" s="268">
+      <c r="P12" s="250">
         <f>$C$12/D12</f>
         <v/>
       </c>
-      <c r="Q12" s="268">
+      <c r="Q12" s="250">
         <f>$C$12/E12</f>
         <v/>
       </c>
-      <c r="R12" s="268">
+      <c r="R12" s="250">
         <f>$C$12/F12</f>
         <v/>
       </c>
-      <c r="S12" s="269">
+      <c r="S12" s="251">
         <f>$C$12/G12</f>
         <v/>
       </c>
-      <c r="T12" s="268">
+      <c r="T12" s="250">
         <f>$C$12/H12</f>
         <v/>
       </c>
-      <c r="U12" s="268">
+      <c r="U12" s="250">
         <f>$C$12/I12</f>
         <v/>
       </c>
-      <c r="V12" s="268">
+      <c r="V12" s="250">
         <f>$C$12/J12</f>
         <v/>
       </c>
-      <c r="W12" s="269">
+      <c r="W12" s="251">
         <f>$C$12/K12</f>
         <v/>
       </c>
-      <c r="X12" s="268">
+      <c r="X12" s="250">
         <f>$C$12/L12</f>
         <v/>
       </c>
-      <c r="Y12" s="268">
+      <c r="Y12" s="250">
         <f>$C$12/M12</f>
         <v/>
       </c>
-      <c r="Z12" s="268">
+      <c r="Z12" s="250">
         <f>$C$12/N12</f>
         <v/>
       </c>
-      <c r="AA12" s="269">
+      <c r="AA12" s="251">
         <f>$C$12/O12</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="14" t="n"/>
-      <c r="C13" s="166" t="n"/>
-      <c r="D13" s="166" t="n"/>
-      <c r="E13" s="166" t="n"/>
-      <c r="F13" s="166" t="n"/>
-      <c r="G13" s="166" t="n"/>
-      <c r="H13" s="166" t="n"/>
-      <c r="I13" s="166" t="n"/>
-      <c r="J13" s="166" t="n"/>
-      <c r="K13" s="166" t="n"/>
-      <c r="L13" s="166" t="n"/>
-      <c r="M13" s="166" t="n"/>
-      <c r="N13" s="166" t="n"/>
-      <c r="O13" s="166" t="n"/>
-      <c r="P13" s="266" t="n"/>
-      <c r="Q13" s="266" t="n"/>
-      <c r="R13" s="266" t="n"/>
-      <c r="S13" s="266" t="n"/>
-      <c r="T13" s="266" t="n"/>
-      <c r="U13" s="266" t="n"/>
-      <c r="V13" s="266" t="n"/>
-      <c r="W13" s="266" t="n"/>
-      <c r="X13" s="266" t="n"/>
-      <c r="Y13" s="266" t="n"/>
-      <c r="Z13" s="266" t="n"/>
-      <c r="AA13" s="266" t="n"/>
+      <c r="C13" s="160" t="n"/>
+      <c r="D13" s="160" t="n"/>
+      <c r="E13" s="160" t="n"/>
+      <c r="F13" s="160" t="n"/>
+      <c r="G13" s="160" t="n"/>
+      <c r="H13" s="160" t="n"/>
+      <c r="I13" s="160" t="n"/>
+      <c r="J13" s="160" t="n"/>
+      <c r="K13" s="160" t="n"/>
+      <c r="L13" s="160" t="n"/>
+      <c r="M13" s="160" t="n"/>
+      <c r="N13" s="160" t="n"/>
+      <c r="O13" s="160" t="n"/>
+      <c r="P13" s="248" t="n"/>
+      <c r="Q13" s="248" t="n"/>
+      <c r="R13" s="248" t="n"/>
+      <c r="S13" s="248" t="n"/>
+      <c r="T13" s="248" t="n"/>
+      <c r="U13" s="248" t="n"/>
+      <c r="V13" s="248" t="n"/>
+      <c r="W13" s="248" t="n"/>
+      <c r="X13" s="248" t="n"/>
+      <c r="Y13" s="248" t="n"/>
+      <c r="Z13" s="248" t="n"/>
+      <c r="AA13" s="248" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="109" t="n"/>
-      <c r="C14" s="110" t="n"/>
-      <c r="D14" s="151" t="inlineStr">
+      <c r="B14" s="106" t="n"/>
+      <c r="C14" s="107" t="n"/>
+      <c r="D14" s="146" t="inlineStr">
         <is>
           <t>Financial Data</t>
         </is>
       </c>
-      <c r="E14" s="151" t="n"/>
-      <c r="F14" s="151" t="n"/>
-      <c r="G14" s="151" t="n"/>
-      <c r="H14" s="152" t="n"/>
-      <c r="I14" s="152" t="n"/>
-      <c r="J14" s="152" t="n"/>
-      <c r="K14" s="153" t="n"/>
-      <c r="L14" s="154" t="n"/>
-      <c r="M14" s="152" t="n"/>
-      <c r="N14" s="152" t="n"/>
-      <c r="O14" s="152" t="n"/>
-      <c r="P14" s="117" t="inlineStr">
+      <c r="E14" s="146" t="n"/>
+      <c r="F14" s="146" t="n"/>
+      <c r="G14" s="146" t="n"/>
+      <c r="H14" s="147" t="n"/>
+      <c r="I14" s="147" t="n"/>
+      <c r="J14" s="147" t="n"/>
+      <c r="K14" s="148" t="n"/>
+      <c r="L14" s="149" t="n"/>
+      <c r="M14" s="147" t="n"/>
+      <c r="N14" s="147" t="n"/>
+      <c r="O14" s="147" t="n"/>
+      <c r="P14" s="114" t="inlineStr">
         <is>
           <t>Implied Enterprise value</t>
         </is>
       </c>
-      <c r="Q14" s="111" t="n"/>
-      <c r="R14" s="111" t="n"/>
-      <c r="S14" s="155" t="n"/>
-      <c r="T14" s="122" t="n"/>
-      <c r="U14" s="122" t="n"/>
-      <c r="V14" s="122" t="n"/>
-      <c r="W14" s="122" t="n"/>
-      <c r="X14" s="122" t="n"/>
-      <c r="Y14" s="122" t="n"/>
-      <c r="Z14" s="122" t="n"/>
-      <c r="AA14" s="123" t="n"/>
+      <c r="Q14" s="108" t="n"/>
+      <c r="R14" s="108" t="n"/>
+      <c r="S14" s="150" t="n"/>
+      <c r="T14" s="119" t="n"/>
+      <c r="U14" s="119" t="n"/>
+      <c r="V14" s="119" t="n"/>
+      <c r="W14" s="119" t="n"/>
+      <c r="X14" s="119" t="n"/>
+      <c r="Y14" s="119" t="n"/>
+      <c r="Z14" s="119" t="n"/>
+      <c r="AA14" s="120" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="126" t="n"/>
-      <c r="C15" s="116" t="inlineStr">
+      <c r="B15" s="123" t="n"/>
+      <c r="C15" s="113" t="inlineStr">
         <is>
           <t>EV</t>
         </is>
       </c>
-      <c r="D15" s="127" t="inlineStr">
+      <c r="D15" s="124" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="E15" s="125" t="n"/>
-      <c r="F15" s="125" t="n"/>
-      <c r="G15" s="128" t="n"/>
-      <c r="H15" s="127" t="inlineStr">
+      <c r="E15" s="122" t="n"/>
+      <c r="F15" s="122" t="n"/>
+      <c r="G15" s="125" t="n"/>
+      <c r="H15" s="124" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="I15" s="125" t="n"/>
-      <c r="J15" s="125" t="n"/>
-      <c r="K15" s="128" t="n"/>
-      <c r="L15" s="127" t="inlineStr">
+      <c r="I15" s="122" t="n"/>
+      <c r="J15" s="122" t="n"/>
+      <c r="K15" s="125" t="n"/>
+      <c r="L15" s="124" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="M15" s="125" t="n"/>
-      <c r="N15" s="125" t="n"/>
-      <c r="O15" s="128" t="n"/>
-      <c r="P15" s="117" t="inlineStr">
+      <c r="M15" s="122" t="n"/>
+      <c r="N15" s="122" t="n"/>
+      <c r="O15" s="125" t="n"/>
+      <c r="P15" s="114" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="Q15" s="112" t="n"/>
-      <c r="R15" s="112" t="n"/>
-      <c r="S15" s="155" t="n"/>
-      <c r="T15" s="117" t="inlineStr">
+      <c r="Q15" s="109" t="n"/>
+      <c r="R15" s="109" t="n"/>
+      <c r="S15" s="150" t="n"/>
+      <c r="T15" s="114" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
-      <c r="U15" s="112" t="n"/>
-      <c r="V15" s="112" t="n"/>
-      <c r="W15" s="155" t="n"/>
-      <c r="X15" s="117" t="inlineStr">
+      <c r="U15" s="109" t="n"/>
+      <c r="V15" s="109" t="n"/>
+      <c r="W15" s="150" t="n"/>
+      <c r="X15" s="114" t="inlineStr">
         <is>
           <t>EV/EBIT</t>
         </is>
       </c>
-      <c r="Y15" s="112" t="n"/>
-      <c r="Z15" s="112" t="n"/>
-      <c r="AA15" s="155" t="n"/>
+      <c r="Y15" s="109" t="n"/>
+      <c r="Z15" s="109" t="n"/>
+      <c r="AA15" s="150" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="115" t="inlineStr">
+      <c r="B16" s="112" t="inlineStr">
         <is>
           <t>Company Name</t>
         </is>
       </c>
-      <c r="C16" s="82" t="n"/>
-      <c r="D16" s="83" t="inlineStr">
+      <c r="C16" s="79" t="n"/>
+      <c r="D16" s="80" t="inlineStr">
         <is>
           <t>(€M)</t>
         </is>
       </c>
-      <c r="E16" s="84" t="n"/>
-      <c r="F16" s="84" t="n"/>
-      <c r="G16" s="85" t="n"/>
-      <c r="H16" s="83" t="inlineStr">
+      <c r="E16" s="81" t="n"/>
+      <c r="F16" s="81" t="n"/>
+      <c r="G16" s="82" t="n"/>
+      <c r="H16" s="80" t="inlineStr">
         <is>
           <t>(€M)</t>
         </is>
       </c>
-      <c r="I16" s="86" t="n"/>
-      <c r="J16" s="86" t="n"/>
-      <c r="K16" s="87" t="n"/>
-      <c r="L16" s="83" t="inlineStr">
+      <c r="I16" s="83" t="n"/>
+      <c r="J16" s="83" t="n"/>
+      <c r="K16" s="84" t="n"/>
+      <c r="L16" s="80" t="inlineStr">
         <is>
           <t>(€M)</t>
         </is>
       </c>
-      <c r="M16" s="84" t="n"/>
-      <c r="N16" s="84" t="n"/>
-      <c r="O16" s="85" t="n"/>
-      <c r="P16" s="90" t="inlineStr">
+      <c r="M16" s="81" t="n"/>
+      <c r="N16" s="81" t="n"/>
+      <c r="O16" s="82" t="n"/>
+      <c r="P16" s="87" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Q16" s="91" t="n"/>
-      <c r="R16" s="91" t="n"/>
-      <c r="S16" s="92" t="n"/>
-      <c r="T16" s="121" t="inlineStr">
+      <c r="Q16" s="88" t="n"/>
+      <c r="R16" s="88" t="n"/>
+      <c r="S16" s="89" t="n"/>
+      <c r="T16" s="118" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="U16" s="122" t="n"/>
-      <c r="V16" s="122" t="n"/>
-      <c r="W16" s="123" t="n"/>
-      <c r="X16" s="121" t="inlineStr">
+      <c r="U16" s="119" t="n"/>
+      <c r="V16" s="119" t="n"/>
+      <c r="W16" s="120" t="n"/>
+      <c r="X16" s="118" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y16" s="122" t="n"/>
-      <c r="Z16" s="122" t="n"/>
-      <c r="AA16" s="123" t="n"/>
+      <c r="Y16" s="119" t="n"/>
+      <c r="Z16" s="119" t="n"/>
+      <c r="AA16" s="120" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="129" t="n"/>
-      <c r="C17" s="93" t="inlineStr">
+      <c r="B17" s="126" t="n"/>
+      <c r="C17" s="90" t="inlineStr">
         <is>
           <t>(€M)</t>
         </is>
       </c>
-      <c r="D17" s="94" t="inlineStr">
+      <c r="D17" s="91" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="E17" s="95" t="inlineStr">
+      <c r="E17" s="92" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="F17" s="95" t="inlineStr">
+      <c r="F17" s="92" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="G17" s="96" t="inlineStr">
+      <c r="G17" s="93" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="H17" s="94" t="inlineStr">
+      <c r="H17" s="91" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="I17" s="95" t="inlineStr">
+      <c r="I17" s="92" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="J17" s="95" t="inlineStr">
+      <c r="J17" s="92" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="K17" s="96" t="inlineStr">
+      <c r="K17" s="93" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="L17" s="94" t="inlineStr">
+      <c r="L17" s="91" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="M17" s="95" t="inlineStr">
+      <c r="M17" s="92" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="N17" s="95" t="inlineStr">
+      <c r="N17" s="92" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="O17" s="96" t="inlineStr">
+      <c r="O17" s="93" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="P17" s="97" t="inlineStr">
+      <c r="P17" s="94" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="Q17" s="97" t="inlineStr">
+      <c r="Q17" s="94" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="R17" s="97" t="inlineStr">
+      <c r="R17" s="94" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="S17" s="98" t="inlineStr">
+      <c r="S17" s="95" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="T17" s="99" t="inlineStr">
+      <c r="T17" s="96" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="U17" s="97" t="inlineStr">
+      <c r="U17" s="94" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="V17" s="97" t="inlineStr">
+      <c r="V17" s="94" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="W17" s="98" t="inlineStr">
+      <c r="W17" s="95" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
-      <c r="X17" s="99" t="inlineStr">
+      <c r="X17" s="96" t="inlineStr">
         <is>
           <t>LFY</t>
         </is>
       </c>
-      <c r="Y17" s="97" t="inlineStr">
+      <c r="Y17" s="94" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="Z17" s="97" t="inlineStr">
+      <c r="Z17" s="94" t="inlineStr">
         <is>
           <t>FY+1</t>
         </is>
       </c>
-      <c r="AA17" s="98" t="inlineStr">
+      <c r="AA17" s="95" t="inlineStr">
         <is>
           <t>FY+2</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="64" t="inlineStr">
+      <c r="B18" s="62" t="inlineStr">
         <is>
           <t>Traton</t>
         </is>
       </c>
-      <c r="C18" s="193" t="n">
+      <c r="C18" s="187" t="n">
         <v>21129</v>
       </c>
-      <c r="D18" s="168" t="n">
+      <c r="D18" s="162" t="n">
         <v>5966</v>
       </c>
-      <c r="E18" s="168" t="n">
+      <c r="E18" s="162" t="n">
         <v>6072</v>
       </c>
-      <c r="F18" s="168" t="n">
+      <c r="F18" s="162" t="n">
         <v>5719</v>
       </c>
-      <c r="G18" s="194" t="n">
+      <c r="G18" s="188" t="n">
         <v>6723</v>
       </c>
-      <c r="H18" s="168" t="n">
+      <c r="H18" s="162" t="n">
         <v>44051</v>
       </c>
-      <c r="I18" s="168" t="n">
+      <c r="I18" s="162" t="n">
         <v>43675</v>
       </c>
-      <c r="J18" s="168" t="n">
+      <c r="J18" s="162" t="n">
         <v>45897</v>
       </c>
-      <c r="K18" s="194" t="n">
+      <c r="K18" s="188" t="n">
         <v>48970</v>
       </c>
-      <c r="L18" s="168" t="n">
+      <c r="L18" s="162" t="n">
         <v>2819</v>
       </c>
-      <c r="M18" s="168" t="n">
+      <c r="M18" s="162" t="n">
         <v>2731</v>
       </c>
-      <c r="N18" s="168" t="n">
+      <c r="N18" s="162" t="n">
         <v>3049</v>
       </c>
-      <c r="O18" s="194" t="n">
+      <c r="O18" s="188" t="n">
         <v>3986</v>
       </c>
-      <c r="P18" s="270">
+      <c r="P18" s="252">
         <f>MEDIAN(P10:P11)*D18</f>
         <v/>
       </c>
-      <c r="Q18" s="271">
+      <c r="Q18" s="253">
         <f>MEDIAN(Q10:Q11)*E18</f>
         <v/>
       </c>
-      <c r="R18" s="271">
+      <c r="R18" s="253">
         <f>MEDIAN(R10:R11)*F18</f>
         <v/>
       </c>
-      <c r="S18" s="272">
+      <c r="S18" s="254">
         <f>MEDIAN(S10:S11)*G18</f>
         <v/>
       </c>
-      <c r="T18" s="271">
+      <c r="T18" s="253">
         <f>MEDIAN(T10:T11)*H18</f>
         <v/>
       </c>
-      <c r="U18" s="271">
+      <c r="U18" s="253">
         <f>MEDIAN(U10:U11)*I18</f>
         <v/>
       </c>
-      <c r="V18" s="271">
+      <c r="V18" s="253">
         <f>MEDIAN(V10:V11)*J18</f>
         <v/>
       </c>
-      <c r="W18" s="272">
+      <c r="W18" s="254">
         <f>MEDIAN(W10:W11)*K18</f>
         <v/>
       </c>
-      <c r="X18" s="271">
+      <c r="X18" s="253">
         <f>MEDIAN(X10:X11)*L18</f>
         <v/>
       </c>
-      <c r="Y18" s="271">
+      <c r="Y18" s="253">
         <f>MEDIAN(Y10:Y11)*M18</f>
         <v/>
       </c>
-      <c r="Z18" s="271">
+      <c r="Z18" s="253">
         <f>MEDIAN(Z10:Z11)*N18</f>
         <v/>
       </c>
-      <c r="AA18" s="272">
+      <c r="AA18" s="254">
         <f>MEDIAN(AA10:AA11)*O18</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="14" t="n"/>
-      <c r="C19" s="103" t="n"/>
-      <c r="D19" s="103" t="n"/>
-      <c r="E19" s="103" t="n"/>
-      <c r="F19" s="103" t="n"/>
-      <c r="G19" s="103" t="n"/>
-      <c r="H19" s="103" t="n"/>
-      <c r="I19" s="103" t="n"/>
-      <c r="J19" s="103" t="n"/>
-      <c r="K19" s="103" t="n"/>
-      <c r="L19" s="103" t="n"/>
-      <c r="M19" s="103" t="n"/>
-      <c r="N19" s="103" t="n"/>
-      <c r="O19" s="103" t="n"/>
-      <c r="P19" s="273" t="n"/>
-      <c r="Q19" s="273" t="n"/>
-      <c r="R19" s="273" t="n"/>
-      <c r="S19" s="273" t="n"/>
-      <c r="T19" s="273" t="n"/>
-      <c r="U19" s="273" t="n"/>
-      <c r="V19" s="273" t="n"/>
-      <c r="W19" s="273" t="n"/>
+      <c r="C19" s="100" t="n"/>
+      <c r="D19" s="100" t="n"/>
+      <c r="E19" s="100" t="n"/>
+      <c r="F19" s="100" t="n"/>
+      <c r="G19" s="100" t="n"/>
+      <c r="H19" s="100" t="n"/>
+      <c r="I19" s="100" t="n"/>
+      <c r="J19" s="100" t="n"/>
+      <c r="K19" s="100" t="n"/>
+      <c r="L19" s="100" t="n"/>
+      <c r="M19" s="100" t="n"/>
+      <c r="N19" s="100" t="n"/>
+      <c r="O19" s="100" t="n"/>
+      <c r="P19" s="255" t="n"/>
+      <c r="Q19" s="255" t="n"/>
+      <c r="R19" s="255" t="n"/>
+      <c r="S19" s="255" t="n"/>
+      <c r="T19" s="255" t="n"/>
+      <c r="U19" s="255" t="n"/>
+      <c r="V19" s="255" t="n"/>
+      <c r="W19" s="255" t="n"/>
       <c r="X19" s="14" t="n"/>
       <c r="Y19" s="14" t="n"/>
       <c r="Z19" s="14" t="n"/>
       <c r="AA19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="148" t="inlineStr">
+      <c r="B20" s="143" t="inlineStr">
         <is>
           <t>Comparison: Company vs. Peer Group</t>
         </is>
       </c>
-      <c r="C20" s="143" t="n"/>
-      <c r="D20" s="103" t="n"/>
-      <c r="E20" s="103" t="n"/>
-      <c r="F20" s="103" t="n"/>
-      <c r="G20" s="103" t="n"/>
-      <c r="H20" s="103" t="n"/>
-      <c r="I20" s="103" t="n"/>
-      <c r="J20" s="103" t="n"/>
-      <c r="K20" s="103" t="n"/>
-      <c r="L20" s="103" t="n"/>
-      <c r="M20" s="103" t="n"/>
-      <c r="N20" s="103" t="n"/>
-      <c r="O20" s="103" t="n"/>
-      <c r="P20" s="273" t="n"/>
-      <c r="Q20" s="273" t="n"/>
-      <c r="R20" s="273" t="n"/>
-      <c r="S20" s="273" t="n"/>
-      <c r="T20" s="273" t="n"/>
-      <c r="U20" s="273" t="n"/>
-      <c r="V20" s="273" t="n"/>
-      <c r="W20" s="273" t="n"/>
+      <c r="C20" s="138" t="n"/>
+      <c r="D20" s="100" t="n"/>
+      <c r="E20" s="100" t="n"/>
+      <c r="F20" s="100" t="n"/>
+      <c r="G20" s="100" t="n"/>
+      <c r="H20" s="100" t="n"/>
+      <c r="I20" s="100" t="n"/>
+      <c r="J20" s="100" t="n"/>
+      <c r="K20" s="100" t="n"/>
+      <c r="L20" s="100" t="n"/>
+      <c r="M20" s="100" t="n"/>
+      <c r="N20" s="100" t="n"/>
+      <c r="O20" s="100" t="n"/>
+      <c r="P20" s="255" t="n"/>
+      <c r="Q20" s="255" t="n"/>
+      <c r="R20" s="255" t="n"/>
+      <c r="S20" s="255" t="n"/>
+      <c r="T20" s="255" t="n"/>
+      <c r="U20" s="255" t="n"/>
+      <c r="V20" s="255" t="n"/>
+      <c r="W20" s="255" t="n"/>
       <c r="X20" s="14" t="n"/>
       <c r="Y20" s="14" t="n"/>
       <c r="Z20" s="14" t="n"/>
       <c r="AA20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="142" t="n"/>
-      <c r="C21" s="172" t="inlineStr">
+      <c r="B21" s="137" t="n"/>
+      <c r="C21" s="166" t="inlineStr">
         <is>
           <t>EV</t>
         </is>
       </c>
-      <c r="D21" s="149" t="inlineStr">
+      <c r="D21" s="144" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="E21" s="149" t="n"/>
-      <c r="F21" s="149" t="n"/>
-      <c r="G21" s="149" t="n"/>
-      <c r="H21" s="149" t="inlineStr">
+      <c r="E21" s="144" t="n"/>
+      <c r="F21" s="144" t="n"/>
+      <c r="G21" s="144" t="n"/>
+      <c r="H21" s="144" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="I21" s="149" t="n"/>
-      <c r="J21" s="149" t="n"/>
-      <c r="K21" s="149" t="n"/>
-      <c r="L21" s="149" t="inlineStr">
+      <c r="I21" s="144" t="n"/>
+      <c r="J21" s="144" t="n"/>
+      <c r="K21" s="144" t="n"/>
+      <c r="L21" s="144" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="M21" s="149" t="n"/>
-      <c r="N21" s="149" t="n"/>
-      <c r="O21" s="149" t="n"/>
-      <c r="P21" s="150" t="inlineStr">
+      <c r="M21" s="144" t="n"/>
+      <c r="N21" s="144" t="n"/>
+      <c r="O21" s="144" t="n"/>
+      <c r="P21" s="145" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="Q21" s="150" t="n"/>
-      <c r="R21" s="150" t="n"/>
-      <c r="S21" s="150" t="n"/>
-      <c r="T21" s="150" t="inlineStr">
+      <c r="Q21" s="145" t="n"/>
+      <c r="R21" s="145" t="n"/>
+      <c r="S21" s="145" t="n"/>
+      <c r="T21" s="145" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
-      <c r="U21" s="150" t="n"/>
-      <c r="V21" s="150" t="n"/>
-      <c r="W21" s="150" t="n"/>
-      <c r="X21" s="150" t="inlineStr">
+      <c r="U21" s="145" t="n"/>
+      <c r="V21" s="145" t="n"/>
+      <c r="W21" s="145" t="n"/>
+      <c r="X21" s="145" t="inlineStr">
         <is>
           <t>EV/EBIT</t>
         </is>
       </c>
-      <c r="Y21" s="150" t="n"/>
-      <c r="Z21" s="150" t="n"/>
-      <c r="AA21" s="150" t="n"/>
+      <c r="Y21" s="145" t="n"/>
+      <c r="Z21" s="145" t="n"/>
+      <c r="AA21" s="145" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="144" t="inlineStr">
+      <c r="B22" s="139" t="inlineStr">
         <is>
           <t>Traton</t>
         </is>
       </c>
-      <c r="C22" s="177" t="n"/>
-      <c r="D22" s="191" t="n"/>
-      <c r="E22" s="173" t="n"/>
-      <c r="F22" s="173" t="n"/>
-      <c r="G22" s="174" t="n"/>
-      <c r="H22" s="173" t="n"/>
-      <c r="I22" s="173" t="n"/>
-      <c r="J22" s="173" t="n"/>
-      <c r="K22" s="174" t="n"/>
-      <c r="L22" s="173" t="n"/>
-      <c r="M22" s="173" t="n"/>
-      <c r="N22" s="173" t="n"/>
-      <c r="O22" s="174" t="n"/>
-      <c r="P22" s="271">
+      <c r="C22" s="171" t="n"/>
+      <c r="D22" s="185" t="n"/>
+      <c r="E22" s="167" t="n"/>
+      <c r="F22" s="167" t="n"/>
+      <c r="G22" s="168" t="n"/>
+      <c r="H22" s="167" t="n"/>
+      <c r="I22" s="167" t="n"/>
+      <c r="J22" s="167" t="n"/>
+      <c r="K22" s="168" t="n"/>
+      <c r="L22" s="167" t="n"/>
+      <c r="M22" s="167" t="n"/>
+      <c r="N22" s="167" t="n"/>
+      <c r="O22" s="168" t="n"/>
+      <c r="P22" s="253">
         <f>P12</f>
         <v/>
       </c>
-      <c r="Q22" s="271">
+      <c r="Q22" s="253">
         <f>Q12</f>
         <v/>
       </c>
-      <c r="R22" s="271">
+      <c r="R22" s="253">
         <f>R12</f>
         <v/>
       </c>
-      <c r="S22" s="272">
+      <c r="S22" s="254">
         <f>S12</f>
         <v/>
       </c>
-      <c r="T22" s="270">
+      <c r="T22" s="252">
         <f>T12</f>
         <v/>
       </c>
-      <c r="U22" s="271">
+      <c r="U22" s="253">
         <f>U12</f>
         <v/>
       </c>
-      <c r="V22" s="271">
+      <c r="V22" s="253">
         <f>V12</f>
         <v/>
       </c>
-      <c r="W22" s="272">
+      <c r="W22" s="254">
         <f>W12</f>
         <v/>
       </c>
-      <c r="X22" s="270">
+      <c r="X22" s="252">
         <f>X12</f>
         <v/>
       </c>
-      <c r="Y22" s="271">
+      <c r="Y22" s="253">
         <f>Y12</f>
         <v/>
       </c>
-      <c r="Z22" s="271">
+      <c r="Z22" s="253">
         <f>Z12</f>
         <v/>
       </c>
-      <c r="AA22" s="272">
+      <c r="AA22" s="254">
         <f>AA12</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="145" t="inlineStr">
+      <c r="B23" s="140" t="inlineStr">
         <is>
           <t>Quartile 1</t>
         </is>
       </c>
-      <c r="C23" s="192" t="n"/>
+      <c r="C23" s="186" t="n"/>
       <c r="D23" s="13" t="n"/>
       <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="n"/>
-      <c r="G23" s="187" t="n"/>
+      <c r="G23" s="181" t="n"/>
       <c r="H23" s="13" t="n"/>
       <c r="I23" s="13" t="n"/>
       <c r="J23" s="13" t="n"/>
-      <c r="K23" s="187" t="n"/>
+      <c r="K23" s="181" t="n"/>
       <c r="L23" s="13" t="n"/>
       <c r="M23" s="13" t="n"/>
       <c r="N23" s="13" t="n"/>
-      <c r="O23" s="187" t="n"/>
-      <c r="P23" s="266">
+      <c r="O23" s="181" t="n"/>
+      <c r="P23" s="248">
         <f>QUARTILE(P10:P11,1)</f>
         <v/>
       </c>
-      <c r="Q23" s="266">
+      <c r="Q23" s="248">
         <f>QUARTILE(Q10:Q11,1)</f>
         <v/>
       </c>
-      <c r="R23" s="266">
+      <c r="R23" s="248">
         <f>QUARTILE(R10:R11,1)</f>
         <v/>
       </c>
-      <c r="S23" s="265">
+      <c r="S23" s="247">
         <f>QUARTILE(S10:S11,1)</f>
         <v/>
       </c>
-      <c r="T23" s="266">
+      <c r="T23" s="248">
         <f>QUARTILE(T10:T11,1)</f>
         <v/>
       </c>
-      <c r="U23" s="266">
+      <c r="U23" s="248">
         <f>QUARTILE(U10:U11,1)</f>
         <v/>
       </c>
-      <c r="V23" s="266">
+      <c r="V23" s="248">
         <f>QUARTILE(V10:V11,1)</f>
         <v/>
       </c>
-      <c r="W23" s="265">
+      <c r="W23" s="247">
         <f>QUARTILE(W10:W11,1)</f>
         <v/>
       </c>
-      <c r="X23" s="266">
+      <c r="X23" s="248">
         <f>QUARTILE(X10:X11,1)</f>
         <v/>
       </c>
-      <c r="Y23" s="266">
+      <c r="Y23" s="248">
         <f>QUARTILE(Y10:Y11,1)</f>
         <v/>
       </c>
-      <c r="Z23" s="266">
+      <c r="Z23" s="248">
         <f>QUARTILE(Z10:Z11,1)</f>
         <v/>
       </c>
-      <c r="AA23" s="265">
+      <c r="AA23" s="247">
         <f>QUARTILE(AA10:AA11,1)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="146" t="inlineStr">
+      <c r="B24" s="141" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="C24" s="178" t="n"/>
+      <c r="C24" s="172" t="n"/>
       <c r="D24" s="13" t="n"/>
       <c r="E24" s="13" t="n"/>
       <c r="F24" s="13" t="n"/>
-      <c r="G24" s="81" t="n"/>
+      <c r="G24" s="78" t="n"/>
       <c r="H24" s="13" t="n"/>
       <c r="I24" s="13" t="n"/>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="81" t="n"/>
+      <c r="K24" s="78" t="n"/>
       <c r="L24" s="13" t="n"/>
       <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
-      <c r="O24" s="81" t="n"/>
-      <c r="P24" s="266">
+      <c r="O24" s="78" t="n"/>
+      <c r="P24" s="248">
         <f>AVERAGE(P10:P11)</f>
         <v/>
       </c>
-      <c r="Q24" s="266">
+      <c r="Q24" s="248">
         <f>AVERAGE(Q10:Q11)</f>
         <v/>
       </c>
-      <c r="R24" s="266">
+      <c r="R24" s="248">
         <f>AVERAGE(R10:R11)</f>
         <v/>
       </c>
-      <c r="S24" s="267">
+      <c r="S24" s="249">
         <f>AVERAGE(S10:S11)</f>
         <v/>
       </c>
-      <c r="T24" s="266">
+      <c r="T24" s="248">
         <f>AVERAGE(T10:T11)</f>
         <v/>
       </c>
-      <c r="U24" s="266">
+      <c r="U24" s="248">
         <f>AVERAGE(U10:U11)</f>
         <v/>
       </c>
-      <c r="V24" s="266">
+      <c r="V24" s="248">
         <f>AVERAGE(V10:V11)</f>
         <v/>
       </c>
-      <c r="W24" s="267">
+      <c r="W24" s="249">
         <f>AVERAGE(W10:W11)</f>
         <v/>
       </c>
-      <c r="X24" s="266">
+      <c r="X24" s="248">
         <f>AVERAGE(X10:X11)</f>
         <v/>
       </c>
-      <c r="Y24" s="266">
+      <c r="Y24" s="248">
         <f>AVERAGE(Y10:Y11)</f>
         <v/>
       </c>
-      <c r="Z24" s="266">
+      <c r="Z24" s="248">
         <f>AVERAGE(Z10:Z11)</f>
         <v/>
       </c>
-      <c r="AA24" s="267">
+      <c r="AA24" s="249">
         <f>AVERAGE(AA10:AA11)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="146" t="inlineStr">
+      <c r="B25" s="141" t="inlineStr">
         <is>
           <t>Median</t>
         </is>
       </c>
-      <c r="C25" s="178" t="n"/>
+      <c r="C25" s="172" t="n"/>
       <c r="D25" s="13" t="n"/>
       <c r="E25" s="13" t="n"/>
       <c r="F25" s="13" t="n"/>
-      <c r="G25" s="81" t="n"/>
+      <c r="G25" s="78" t="n"/>
       <c r="H25" s="13" t="n"/>
       <c r="I25" s="13" t="n"/>
       <c r="J25" s="13" t="n"/>
-      <c r="K25" s="81" t="n"/>
+      <c r="K25" s="78" t="n"/>
       <c r="L25" s="13" t="n"/>
       <c r="M25" s="13" t="n"/>
       <c r="N25" s="13" t="n"/>
-      <c r="O25" s="81" t="n"/>
-      <c r="P25" s="266">
+      <c r="O25" s="78" t="n"/>
+      <c r="P25" s="248">
         <f>MEDIAN(P10:P11)</f>
         <v/>
       </c>
-      <c r="Q25" s="266">
+      <c r="Q25" s="248">
         <f>MEDIAN(Q10:Q11)</f>
         <v/>
       </c>
-      <c r="R25" s="266">
+      <c r="R25" s="248">
         <f>MEDIAN(R10:R11)</f>
         <v/>
       </c>
-      <c r="S25" s="267">
+      <c r="S25" s="249">
         <f>MEDIAN(S10:S11)</f>
         <v/>
       </c>
-      <c r="T25" s="266">
+      <c r="T25" s="248">
         <f>MEDIAN(T10:T11)</f>
         <v/>
       </c>
-      <c r="U25" s="266">
+      <c r="U25" s="248">
         <f>MEDIAN(U10:U11)</f>
         <v/>
       </c>
-      <c r="V25" s="266">
+      <c r="V25" s="248">
         <f>MEDIAN(V10:V11)</f>
         <v/>
       </c>
-      <c r="W25" s="267">
+      <c r="W25" s="249">
         <f>MEDIAN(W10:W11)</f>
         <v/>
       </c>
-      <c r="X25" s="266">
+      <c r="X25" s="248">
         <f>MEDIAN(X10:X11)</f>
         <v/>
       </c>
-      <c r="Y25" s="266">
+      <c r="Y25" s="248">
         <f>MEDIAN(Y10:Y11)</f>
         <v/>
       </c>
-      <c r="Z25" s="266">
+      <c r="Z25" s="248">
         <f>MEDIAN(Z10:Z11)</f>
         <v/>
       </c>
-      <c r="AA25" s="267">
+      <c r="AA25" s="249">
         <f>MEDIAN(AA10:AA11)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="147" t="inlineStr">
+      <c r="B26" s="142" t="inlineStr">
         <is>
           <t>Quartile 3</t>
         </is>
       </c>
-      <c r="C26" s="179" t="n"/>
-      <c r="D26" s="188" t="n"/>
-      <c r="E26" s="190" t="n"/>
-      <c r="F26" s="190" t="n"/>
-      <c r="G26" s="189" t="n"/>
-      <c r="H26" s="190" t="n"/>
-      <c r="I26" s="190" t="n"/>
-      <c r="J26" s="190" t="n"/>
-      <c r="K26" s="189" t="n"/>
-      <c r="L26" s="190" t="n"/>
-      <c r="M26" s="190" t="n"/>
-      <c r="N26" s="190" t="n"/>
-      <c r="O26" s="189" t="n"/>
-      <c r="P26" s="268">
+      <c r="C26" s="173" t="n"/>
+      <c r="D26" s="182" t="n"/>
+      <c r="E26" s="184" t="n"/>
+      <c r="F26" s="184" t="n"/>
+      <c r="G26" s="183" t="n"/>
+      <c r="H26" s="184" t="n"/>
+      <c r="I26" s="184" t="n"/>
+      <c r="J26" s="184" t="n"/>
+      <c r="K26" s="183" t="n"/>
+      <c r="L26" s="184" t="n"/>
+      <c r="M26" s="184" t="n"/>
+      <c r="N26" s="184" t="n"/>
+      <c r="O26" s="183" t="n"/>
+      <c r="P26" s="250">
         <f>QUARTILE(P10:P11,3)</f>
         <v/>
       </c>
-      <c r="Q26" s="268">
+      <c r="Q26" s="250">
         <f>QUARTILE(Q10:Q11,3)</f>
         <v/>
       </c>
-      <c r="R26" s="268">
+      <c r="R26" s="250">
         <f>QUARTILE(R10:R11,3)</f>
         <v/>
       </c>
-      <c r="S26" s="269">
+      <c r="S26" s="251">
         <f>QUARTILE(S10:S11,3)</f>
         <v/>
       </c>
-      <c r="T26" s="274">
+      <c r="T26" s="256">
         <f>QUARTILE(T10:T11,3)</f>
         <v/>
       </c>
-      <c r="U26" s="268">
+      <c r="U26" s="250">
         <f>QUARTILE(U10:U11,3)</f>
         <v/>
       </c>
-      <c r="V26" s="268">
+      <c r="V26" s="250">
         <f>QUARTILE(V10:V11,3)</f>
         <v/>
       </c>
-      <c r="W26" s="269">
+      <c r="W26" s="251">
         <f>QUARTILE(W10:W11,3)</f>
         <v/>
       </c>
-      <c r="X26" s="274">
+      <c r="X26" s="256">
         <f>QUARTILE(X10:X11,3)</f>
         <v/>
       </c>
-      <c r="Y26" s="268">
+      <c r="Y26" s="250">
         <f>QUARTILE(Y10:Y11,3)</f>
         <v/>
       </c>
-      <c r="Z26" s="268">
+      <c r="Z26" s="250">
         <f>QUARTILE(Z10:Z11,3)</f>
         <v/>
       </c>
-      <c r="AA26" s="269">
+      <c r="AA26" s="251">
         <f>QUARTILE(AA10:AA11,3)</f>
         <v/>
       </c>
@@ -6273,115 +7258,116 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="I3:L9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11" customWidth="1" style="1" min="1" max="8"/>
-    <col width="26.7109375" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="5.5703125" bestFit="1" customWidth="1" style="1" min="10" max="11"/>
-    <col width="6.5703125" bestFit="1" customWidth="1" style="1" min="12" max="12"/>
-    <col width="11" customWidth="1" style="1" min="13" max="16384"/>
+    <col width="11" customWidth="1" style="196" min="1" max="8"/>
+    <col width="26.6640625" bestFit="1" customWidth="1" style="196" min="9" max="9"/>
+    <col width="5.5546875" bestFit="1" customWidth="1" style="196" min="10" max="11"/>
+    <col width="6.5546875" bestFit="1" customWidth="1" style="196" min="12" max="12"/>
+    <col width="11" customWidth="1" style="196" min="13" max="13"/>
+    <col width="11" customWidth="1" style="196" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="3">
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="196" t="inlineStr">
         <is>
           <t>Valuation method</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="196" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" s="196" t="inlineStr">
         <is>
           <t>diff</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" s="196" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="196" t="inlineStr">
         <is>
           <t>DCF (WACC 6.9-7.9%)</t>
         </is>
       </c>
-      <c r="J4" s="163" t="n">
+      <c r="J4" s="157" t="n">
         <v>55.4</v>
       </c>
-      <c r="K4" s="163">
+      <c r="K4" s="157">
         <f>L4-J4</f>
         <v/>
       </c>
-      <c r="L4" s="163" t="n">
+      <c r="L4" s="157" t="n">
         <v>67.40000000000001</v>
       </c>
     </row>
     <row r="5">
-      <c r="I5" s="1" t="inlineStr">
+      <c r="I5" s="196" t="inlineStr">
         <is>
           <t>EV/EBITDA FY+1 (peer range)</t>
         </is>
       </c>
-      <c r="J5" s="163" t="n">
+      <c r="J5" s="157" t="n">
         <v>48.7</v>
       </c>
-      <c r="K5" s="163">
+      <c r="K5" s="157">
         <f>L5-J5</f>
         <v/>
       </c>
-      <c r="L5" s="163" t="n">
+      <c r="L5" s="157" t="n">
         <v>80.90000000000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="I6" s="1" t="inlineStr">
+      <c r="I6" s="196" t="inlineStr">
         <is>
           <t>EV/EBIT FY+1 (peer range)</t>
         </is>
       </c>
-      <c r="J6" s="163" t="n">
+      <c r="J6" s="157" t="n">
         <v>30.2</v>
       </c>
-      <c r="K6" s="163">
+      <c r="K6" s="157">
         <f>L6-J6</f>
         <v/>
       </c>
-      <c r="L6" s="163" t="n">
+      <c r="L6" s="157" t="n">
         <v>56.9</v>
       </c>
     </row>
     <row r="7">
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I7" s="196" t="inlineStr">
         <is>
           <t>EV/Revenue FY+1 (peer range)</t>
         </is>
       </c>
-      <c r="J7" s="163" t="n">
+      <c r="J7" s="157" t="n">
         <v>34.3</v>
       </c>
-      <c r="K7" s="163">
+      <c r="K7" s="157">
         <f>L7-J7</f>
         <v/>
       </c>
-      <c r="L7" s="163" t="n">
+      <c r="L7" s="157" t="n">
         <v>107.2</v>
       </c>
     </row>
     <row r="8">
-      <c r="K8" s="163" t="n"/>
-      <c r="L8" s="163" t="n"/>
+      <c r="K8" s="157" t="n"/>
+      <c r="L8" s="157" t="n"/>
     </row>
     <row r="9">
       <c r="I9" t="inlineStr">
@@ -6392,8 +7378,8 @@
       <c r="J9" t="n">
         <v>33.18</v>
       </c>
-      <c r="K9" s="163" t="n"/>
-      <c r="L9" s="163" t="n"/>
+      <c r="K9" s="157" t="n"/>
+      <c r="L9" s="157" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
